--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_correct_values.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_correct_values.xlsx
@@ -140,7 +140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -149,7 +149,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -766,25 +766,25 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>136.2</v>
+        <v>186.2</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>28.1</v>
+        <v>28.6</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>20.9</v>
+        <v>20.5</v>
       </c>
       <c r="F4" s="10" t="n">
         <v>24.1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>81.7</v>
+        <v>87.2</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1.7</v>
+        <v>11.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>2.9</v>
@@ -808,13 +808,13 @@
         <v>0.2</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>22.1</v>
+        <v>27.1</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>68.90000000000001</v>
@@ -826,13 +826,13 @@
         <v>25.2</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>82.8</v>
+        <v>22.8</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>181.8</v>
+        <v>81.8</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>5.8</v>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>203.8</v>
+        <v>403.8</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>32.6</v>
@@ -875,7 +875,7 @@
         <v>5.5</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>18.9</v>
@@ -887,7 +887,7 @@
         <v>21.6</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>909</v>
+        <v>99</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0.2</v>
@@ -913,11 +913,11 @@
       <c r="W5" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X5" s="11" t="n">
-        <v>72.8</v>
+      <c r="X5" s="3" t="n">
+        <v>27.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>141.1</v>
+        <v>7174</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>8.199999999999999</v>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>122.3</v>
+        <v>422.3</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>34.2</v>
@@ -950,8 +950,8 @@
       <c r="G6" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="H6" s="11" t="n">
-        <v>184.6</v>
+      <c r="H6" s="8" t="n">
+        <v>15.2</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>14.6</v>
@@ -974,8 +974,8 @@
       <c r="O6" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="P6" s="11" t="n">
-        <v>80</v>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>32.7</v>
@@ -987,22 +987,22 @@
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>22.8</v>
+        <v>92.8</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="W6" s="11" t="n">
-        <v>31.7</v>
+        <v>28.1</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>23.7</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>16614.1</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>13.2</v>
@@ -1021,16 +1021,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6472.5</v>
+        <v>472.5</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>7.3</v>
+        <v>19.3</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>15.4</v>
@@ -1039,10 +1039,10 @@
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>47.9</v>
+        <v>84.7</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.9</v>
+        <v>7.9</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
@@ -1066,7 +1066,7 @@
         <v>34.2</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>27.1</v>
@@ -1077,7 +1077,7 @@
       <c r="U7" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="V7" s="11" t="n">
+      <c r="V7" s="3" t="n">
         <v>29.5</v>
       </c>
       <c r="W7" s="3" t="n">
@@ -1090,7 +1090,7 @@
         <v>66.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>15.8</v>
+        <v>13.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1120,14 +1120,14 @@
       <c r="G8" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="H8" s="8" t="n">
         <v>12</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>30.9</v>
@@ -1142,7 +1142,7 @@
         <v>24</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>96.5</v>
+        <v>296.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.8</v>
@@ -1172,7 +1172,7 @@
         <v>26.1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>20.6</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1781.2</v>
+        <v>1783.2</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>164.8</v>
@@ -1200,19 +1200,19 @@
         <v>96.90000000000001</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>1301.7</v>
+        <v>230.8</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>12.8</v>
+        <v>27.5</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>30.9</v>
@@ -1227,40 +1227,40 @@
         <v>112.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>894.2</v>
+        <v>494.2</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1179.6</v>
+        <v>149.6</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>122.9</v>
+        <v>121.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>155.1</v>
+        <v>135.7</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>329.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>132.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1116.8</v>
+        <v>116.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>133.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>388.8</v>
+        <v>3788.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>141.6</v>
+        <v>41.6</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8188.5</v>
+        <v>35.4</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>33</v>
@@ -1285,21 +1285,23 @@
         <v>19.4</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>11.9</v>
+        <v>17.9</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
+        <v>5.5</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>20</v>
       </c>
@@ -1315,14 +1317,14 @@
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="8" t="n">
         <v>29.9</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>27.8</v>
+        <v>27.1</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>66</v>
@@ -1336,14 +1338,14 @@
       <c r="W10" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="X10" s="11" t="n">
-        <v>16.2</v>
+      <c r="X10" s="3" t="n">
+        <v>26.7</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>72.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>18.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1359,7 +1361,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1265.6</v>
+        <v>265.6</v>
       </c>
       <c r="D11" s="10" t="n">
         <v>30</v>
@@ -1377,7 +1379,7 @@
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.8</v>
@@ -1392,10 +1394,10 @@
         <v>20.9</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>927.3</v>
+        <v>21.3</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.6</v>
@@ -1404,31 +1406,31 @@
         <v>29.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="S11" s="11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="S11" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>720.6</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V11" s="11" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="W11" s="11" t="n">
-        <v>16.9</v>
+      <c r="V11" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>94.90000000000001</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>2894</v>
+        <v>894</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>11.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1444,15 +1446,15 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>347.1</v>
+        <v>242.1</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>91.8</v>
+        <v>31.8</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>32.6</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="10" t="n">
         <v>27.2</v>
       </c>
       <c r="G12" s="3" t="n">
@@ -1461,8 +1463,8 @@
       <c r="H12" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="I12" s="11" t="n">
-        <v>227.1</v>
+      <c r="I12" s="3" t="n">
+        <v>2.7</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>14.6</v>
@@ -1473,14 +1475,14 @@
       <c r="L12" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="11" t="n">
-        <v>350.5</v>
-      </c>
-      <c r="N12" s="11" t="n">
-        <v>17.9</v>
+      <c r="M12" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>27.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>927.5</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.5</v>
@@ -1492,10 +1494,10 @@
         <v>24.9</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>21.1</v>
+        <v>27.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>51.8</v>
+        <v>59.8</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>19.8</v>
@@ -1513,7 +1515,7 @@
         <v>76.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>21.6</v>
+        <v>81.7</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1547,10 +1549,10 @@
         <v>19.9</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>18.3</v>
+        <v>3.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
@@ -1576,11 +1578,11 @@
       <c r="R13" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="S13" s="11" t="n">
-        <v>21.8</v>
+      <c r="S13" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>427.4</v>
+        <v>52.7</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>23.3</v>
@@ -1592,7 +1594,7 @@
         <v>24.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>77.59999999999999</v>
@@ -1632,12 +1634,14 @@
         <v>20.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
+        <v>82.09999999999999</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="L14" s="3" t="n">
         <v>22.4</v>
       </c>
@@ -1671,8 +1675,8 @@
       <c r="V14" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W14" s="11" t="n">
-        <v>211.6</v>
+      <c r="W14" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>25.5</v>
@@ -1680,9 +1684,7 @@
       <c r="Y14" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="Z14" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="Z14" s="3" t="inlineStr"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1697,7 +1699,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>282.8</v>
+        <v>359.6</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>32.6</v>
@@ -1708,35 +1710,35 @@
       <c r="F15" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="8" t="n">
         <v>11.7</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K15" s="11" t="n">
-        <v>51.7</v>
+      <c r="K15" s="3" t="n">
+        <v>23.7</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" s="11" t="n">
+      <c r="M15" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>32</v>
@@ -1763,10 +1765,10 @@
         <v>28.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>738.1</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>100.6</v>
+        <v>10.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1782,16 +1784,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1291.2</v>
+        <v>1221.2</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>167.9</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>105.5</v>
+        <v>1255.1</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>151.4</v>
+        <v>131.9</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>52.4</v>
@@ -1809,16 +1811,16 @@
         <v>36.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1110.6</v>
+        <v>110.6</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>109.5</v>
+        <v>109.8</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>1230.7</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>2490.1</v>
+        <v>1490.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.2</v>
@@ -1827,10 +1829,10 @@
         <v>148.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>121.9</v>
+        <v>1221.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1136.2</v>
+        <v>1136.1</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>331.8</v>
@@ -1869,14 +1871,14 @@
       <c r="C17" s="3" t="n">
         <v>318.2</v>
       </c>
-      <c r="D17" s="9" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>26.3</v>
+      <c r="D17" s="10" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>26.4</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>10.5</v>
@@ -1885,13 +1887,13 @@
         <v>19.8</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K17" s="3" t="n">
-        <v>1.1</v>
+      <c r="K17" s="8" t="n">
+        <v>6</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>22.1</v>
@@ -1903,13 +1905,13 @@
         <v>26.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>398</v>
+        <v>928</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>29.1</v>
+        <v>29.7</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>24.4</v>
@@ -1921,16 +1923,16 @@
         <v>66.40000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W17" s="11" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="X17" s="11" t="n">
-        <v>84.59999999999999</v>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>28.5</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>81.5</v>
@@ -1954,18 +1956,16 @@
       <c r="C18" s="3" t="n">
         <v>368</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="10" t="n">
         <v>32.1</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>21.2</v>
       </c>
-      <c r="F18" s="12" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="F18" s="10" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="n">
         <v>80.40000000000001</v>
       </c>
@@ -1973,10 +1973,10 @@
         <v>2.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K18" s="11" t="n">
-        <v>6.4</v>
+        <v>14.3</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>10.4</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>21.4</v>
@@ -1984,11 +1984,11 @@
       <c r="M18" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="N18" s="11" t="n">
-        <v>12.8</v>
+      <c r="N18" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>91.3</v>
+        <v>97.3</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
@@ -1996,14 +1996,14 @@
       <c r="Q18" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="11" t="n">
+      <c r="R18" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>27.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>20</v>
@@ -2018,10 +2018,10 @@
         <v>21.9</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2051,8 +2051,8 @@
       <c r="G19" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H19" s="3" t="n">
-        <v>21.4</v>
+      <c r="H19" s="8" t="n">
+        <v>91.40000000000001</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.6</v>
@@ -2076,16 +2076,16 @@
         <v>97.59999999999999</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="Q19" s="11" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Q19" s="8" t="n">
         <v>29.9</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>26</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>51.1</v>
+        <v>31.1</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>73.7</v>
@@ -2093,20 +2093,20 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="11" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="W19" s="11" t="n">
-        <v>289.8</v>
+      <c r="V19" s="3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="W19" s="8" t="n">
+        <v>28.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>24.1</v>
+        <v>27.1</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>829</v>
+        <v>89</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>185.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2122,16 +2122,16 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3865.9</v>
-      </c>
-      <c r="D20" s="10" t="n">
+        <v>365.9</v>
+      </c>
+      <c r="D20" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="E20" s="10" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F20" s="10" t="n">
-        <v>26.4</v>
+      <c r="E20" s="8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>28.5</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>19.9</v>
@@ -2140,13 +2140,13 @@
         <v>20.6</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>21.6</v>
@@ -2158,19 +2158,19 @@
         <v>25.4</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>928</v>
+        <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>20.9</v>
+        <v>30.7</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="S20" s="3" t="n">
-        <v>27.5</v>
+      <c r="S20" s="8" t="n">
+        <v>17.5</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>12.3</v>
@@ -2181,17 +2181,17 @@
       <c r="V20" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="W20" s="11" t="n">
-        <v>28.8</v>
+      <c r="W20" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>21.2</v>
+        <v>27.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>125</v>
+        <v>725</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2209,13 +2209,13 @@
       <c r="C21" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D21" s="10" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F21" s="10" t="n">
+      <c r="D21" s="8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F21" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -2237,10 +2237,10 @@
         <v>21.6</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>21.9</v>
+        <v>21.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>23.6</v>
+        <v>25.6</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>99</v>
@@ -2255,7 +2255,7 @@
         <v>26.2</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>91.2</v>
+        <v>31.2</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>71.2</v>
@@ -2266,14 +2266,14 @@
       <c r="V21" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W21" s="11" t="n">
-        <v>46.6</v>
+      <c r="W21" s="8" t="n">
+        <v>26.6</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>712.3</v>
+        <v>72.3</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>8.4</v>
@@ -2304,7 +2304,7 @@
         <v>27</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>19.8</v>
@@ -2316,13 +2316,13 @@
         <v>4.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>24.7</v>
@@ -2337,7 +2337,7 @@
         <v>32.4</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>25.9</v>
+        <v>29.9</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>89.3</v>
@@ -2346,22 +2346,22 @@
         <v>60.5</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="V22" s="3" t="n">
-        <v>86.5</v>
+        <v>19.2</v>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v>26.5</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X22" s="11" t="n">
-        <v>29.4</v>
+      <c r="X22" s="3" t="n">
+        <v>29.7</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>86</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1244.9</v>
+        <v>144.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2377,19 +2377,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>8519.6</v>
+        <v>1739.6</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1468.5</v>
+        <v>167.5</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1074.2</v>
+        <v>107.2</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>132.4</v>
+        <v>138.8</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>50.3</v>
+        <v>20.3</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>101.8</v>
@@ -2398,10 +2398,10 @@
         <v>10.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>104.5</v>
+        <v>10.4</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>495.1</v>
+        <v>49.1</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>108.2</v>
@@ -2419,7 +2419,7 @@
         <v>2.2</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1565.7</v>
+        <v>155.7</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>128.1</v>
@@ -2428,16 +2428,16 @@
         <v>146.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>3325.1</v>
+        <v>325.1</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>138.4</v>
+        <v>134.4</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>120.3</v>
+        <v>20.3</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>140.8</v>
@@ -2446,7 +2446,7 @@
         <v>399</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>362.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2462,13 +2462,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>343.9</v>
+        <v>343.2</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>31.6</v>
+        <v>31.2</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>21.5</v>
+        <v>21.1</v>
       </c>
       <c r="F24" s="10" t="n">
         <v>26.4</v>
@@ -2480,13 +2480,13 @@
         <v>20.4</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>21.6</v>
@@ -2507,10 +2507,10 @@
         <v>31.1</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>25.6</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>29.4</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>65.09999999999999</v>
@@ -2524,14 +2524,14 @@
       <c r="W24" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="X24" s="11" t="n">
-        <v>29.2</v>
+      <c r="X24" s="3" t="n">
+        <v>23.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>79.8</v>
+        <v>2981.3</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>23.5</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>20.2</v>
@@ -2571,7 +2571,7 @@
         <v>0.5</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>23.4</v>
+        <v>23.7</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>22.4</v>
@@ -2583,7 +2583,7 @@
         <v>26.4</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>914</v>
+        <v>97</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0.7</v>
@@ -2592,7 +2592,7 @@
         <v>26.2</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>24.1</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>28.7</v>
@@ -2601,17 +2601,19 @@
         <v>84.40000000000001</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="V25" s="3" t="inlineStr"/>
+        <v>5.3</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>14.4</v>
+      </c>
       <c r="W25" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X25" s="11" t="n">
+      <c r="X25" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>8417.4</v>
+        <v>8781.700000000001</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2630,26 +2632,26 @@
       <c r="C26" s="3" t="n">
         <v>290</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="10" t="n">
         <v>25.1</v>
       </c>
-      <c r="E26" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="F26" s="3" t="n">
+      <c r="E26" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="F26" s="10" t="n">
         <v>23.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>12.1</v>
+        <v>14.1</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>6.1</v>
@@ -2661,7 +2663,7 @@
         <v>21.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>100</v>
@@ -2673,13 +2675,13 @@
         <v>24.3</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>28</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>92</v>
+        <v>192</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>2.4</v>
@@ -2690,14 +2692,14 @@
       <c r="W26" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X26" s="11" t="n">
-        <v>71.09999999999999</v>
+      <c r="X26" s="3" t="n">
+        <v>27.1</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>91.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>124.5</v>
+        <v>2.4</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2715,14 +2717,14 @@
       <c r="C27" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D27" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E27" s="3" t="n">
+      <c r="D27" s="10" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E27" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="F27" s="12" t="n">
-        <v>35.4</v>
+      <c r="F27" s="10" t="n">
+        <v>25.5</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>19.9</v>
@@ -2740,7 +2742,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>20.5</v>
@@ -2757,8 +2759,8 @@
       <c r="Q27" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R27" s="11" t="n">
-        <v>16.9</v>
+      <c r="R27" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>29</v>
@@ -2769,20 +2771,20 @@
       <c r="U27" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="V27" s="3" t="n">
-        <v>86.90000000000001</v>
+      <c r="V27" s="8" t="n">
+        <v>826.9</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="X27" s="11" t="n">
-        <v>289</v>
+        <v>24.4</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>89</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>81.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>12.4</v>
+        <v>6.4</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2800,16 +2802,16 @@
       <c r="C28" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D28" s="12" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="E28" s="3" t="n">
+      <c r="D28" s="10" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E28" s="10" t="n">
         <v>20.5</v>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="F28" s="10" t="n">
         <v>26.1</v>
       </c>
-      <c r="G28" s="11" t="n">
+      <c r="G28" s="8" t="n">
         <v>11.3</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2834,10 +2836,10 @@
         <v>24.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>97.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>31.2</v>
@@ -2867,7 +2869,7 @@
         <v>72.59999999999999</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>107.4</v>
+        <v>10.7</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2885,16 +2887,16 @@
       <c r="C29" s="3" t="n">
         <v>246.8</v>
       </c>
-      <c r="D29" s="11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="E29" s="3" t="n">
+      <c r="D29" s="10" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E29" s="10" t="n">
         <v>20.5</v>
       </c>
-      <c r="F29" s="12" t="n">
-        <v>96</v>
-      </c>
-      <c r="G29" s="11" t="n">
+      <c r="F29" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="G29" s="8" t="n">
         <v>11</v>
       </c>
       <c r="H29" s="3" t="n">
@@ -2904,7 +2906,7 @@
         <v>1.6</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>8.4</v>
@@ -2925,7 +2927,7 @@
         <v>1.1</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>25.3</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>23.6</v>
@@ -2934,10 +2936,10 @@
         <v>28</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>14.2</v>
+        <v>94.2</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>22.4</v>
@@ -2945,8 +2947,8 @@
       <c r="W29" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="X29" s="11" t="n">
-        <v>16.6</v>
+      <c r="X29" s="8" t="n">
+        <v>14.6</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>90.8</v>
@@ -2970,20 +2972,20 @@
       <c r="C30" s="3" t="n">
         <v>11056.2</v>
       </c>
-      <c r="D30" s="9" t="n">
-        <v>1145.2</v>
-      </c>
-      <c r="E30" s="9" t="n">
+      <c r="D30" s="10" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="E30" s="10" t="n">
         <v>103.2</v>
       </c>
-      <c r="F30" s="9" t="n">
-        <v>1124.2</v>
+      <c r="F30" s="10" t="n">
+        <v>124.2</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>42</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>196.6</v>
+        <v>296.6</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>7.1</v>
@@ -2992,7 +2994,7 @@
         <v>111</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>28.8</v>
+        <v>328.8</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>106.5</v>
@@ -3001,7 +3003,7 @@
         <v>105.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>125.9</v>
+        <v>123.9</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>487.6</v>
@@ -3013,31 +3015,29 @@
         <v>1135.8</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>120.1</v>
+        <v>120.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>140.9</v>
+        <v>1240.9</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>396.8</v>
       </c>
-      <c r="U30" s="3" t="n">
-        <v>18</v>
-      </c>
+      <c r="U30" s="3" t="inlineStr"/>
       <c r="V30" s="3" t="n">
-        <v>1126.1</v>
+        <v>126.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>115.8</v>
+        <v>115.9</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>132.9</v>
+        <v>135.9</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>1424.7</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>28.1</v>
+        <v>85.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3055,14 +3055,14 @@
       <c r="C31" s="3" t="n">
         <v>211.2</v>
       </c>
-      <c r="D31" s="12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>14.8</v>
+      <c r="D31" s="9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>8.4</v>
@@ -3077,7 +3077,7 @@
         <v>2.2</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>21.3</v>
@@ -3089,7 +3089,7 @@
         <v>24.8</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>97.5</v>
+        <v>927.5</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>0.6</v>
@@ -3107,7 +3107,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>18.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>25.2</v>
@@ -3116,13 +3116,13 @@
         <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>97.2</v>
+        <v>27.2</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>24.9</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3138,25 +3138,25 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>8816.9</v>
+        <v>384.7</v>
       </c>
       <c r="D32" s="10" t="n">
         <v>31.1</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>19.3</v>
+        <v>15.3</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>25.2</v>
+        <v>23.2</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="H32" s="11" t="n">
+      <c r="H32" s="8" t="n">
         <v>18</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>4.6</v>
@@ -3171,7 +3171,7 @@
         <v>20.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>100</v>
@@ -3185,26 +3185,26 @@
       <c r="R32" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S32" s="11" t="n">
-        <v>72.5</v>
+      <c r="S32" s="3" t="n">
+        <v>27.5</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>61</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>27.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>23.8</v>
+        <v>83.8</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>97.2</v>
+        <v>27.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>7641.6</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>19.3</v>
@@ -3250,13 +3250,13 @@
         <v>14.8</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>81.5</v>
+        <v>21.5</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>17.8</v>
+        <v>23.9</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>99</v>
@@ -3265,16 +3265,16 @@
         <v>0.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>22.9</v>
+        <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>20.6</v>
+        <v>28.6</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>20.9</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>11.5</v>
@@ -3282,17 +3282,17 @@
       <c r="V33" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="W33" s="11" t="n">
+      <c r="W33" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>28.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>86.2</v>
+        <v>26.1</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>12.5</v>
+        <v>144.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3314,13 +3314,13 @@
         <v>31.9</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>20.2</v>
@@ -3329,7 +3329,7 @@
         <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>39.5</v>
+        <v>9.5</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.2</v>
@@ -3350,10 +3350,10 @@
         <v>0.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>3</v>
+        <v>30.5</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>23.8</v>
+        <v>25.8</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>30.2</v>
@@ -3374,7 +3374,7 @@
         <v>29.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>182.8</v>
+        <v>82.8</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>16.5</v>
@@ -3399,7 +3399,7 @@
         <v>31.1</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>25.9</v>
@@ -3432,16 +3432,16 @@
         <v>97.2</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="3" t="n">
-        <v>24.9</v>
+      <c r="R35" s="8" t="n">
+        <v>46.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>27.8</v>
+        <v>21.8</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>61.3</v>
@@ -3450,19 +3450,19 @@
         <v>17.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W35" s="11" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="W35" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>811.1</v>
+        <v>8.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
       <c r="F36" s="10" t="n">
         <v>26.5</v>
       </c>
-      <c r="G36" s="11" t="n">
+      <c r="G36" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3514,7 +3514,7 @@
         <v>24.2</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>98.5</v>
+        <v>97.5</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.6</v>
@@ -3537,17 +3537,17 @@
       <c r="V36" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X36" s="11" t="n">
-        <v>83.90000000000001</v>
+      <c r="W36" s="8" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>28.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>172</v>
+        <v>72</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>11</v>
+        <v>1411</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3593,10 +3593,10 @@
         <v>1106</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>105.2</v>
+        <v>103.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>126.1</v>
+        <v>124.1</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>492.7</v>
@@ -3605,7 +3605,7 @@
         <v>17.1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>153.1</v>
+        <v>153.7</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>126.2</v>
@@ -3614,25 +3614,25 @@
         <v>143.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>8216.799999999999</v>
+        <v>324.8</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>11.7</v>
+        <v>19.7</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>126.8</v>
+        <v>136.8</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>102.4</v>
+        <v>122.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>398.2</v>
+        <v>3928.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>892.1</v>
+        <v>39.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>2</v>
@@ -3690,20 +3690,20 @@
       <c r="Q38" s="3" t="n">
         <v>30.7</v>
       </c>
-      <c r="R38" s="11" t="n">
+      <c r="R38" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>27.4</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>24.3</v>
@@ -3715,7 +3715,7 @@
         <v>78</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>566.1</v>
+        <v>7.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3731,21 +3731,21 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>3232.5</v>
-      </c>
-      <c r="D39" s="12" t="n">
-        <v>821.8100000000001</v>
-      </c>
-      <c r="E39" s="3" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E39" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="F39" s="3" t="n">
+      <c r="F39" s="10" t="n">
         <v>26.1</v>
       </c>
-      <c r="G39" s="11" t="n">
+      <c r="G39" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="H39" s="3" t="n">
+      <c r="H39" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3755,7 +3755,7 @@
         <v>3</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>21</v>
@@ -3773,9 +3773,9 @@
         <v>0.2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="R39" s="11" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="R39" s="3" t="n">
         <v>26</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3785,13 +3785,13 @@
         <v>163.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="V39" s="11" t="n">
-        <v>49.1</v>
+        <v>11.3</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>22.2</v>
+        <v>23.2</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>2.7</v>
@@ -3800,7 +3800,7 @@
         <v>88.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>8.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3816,15 +3816,15 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1534.1</v>
-      </c>
-      <c r="D40" s="12" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="E40" s="3" t="n">
+        <v>153.7</v>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="E40" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="F40" s="3" t="n">
+      <c r="F40" s="10" t="n">
         <v>25.9</v>
       </c>
       <c r="G40" s="3" t="n">
@@ -3834,10 +3834,10 @@
         <v>18.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
         <v>29.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>39.2</v>
+        <v>59.2</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>20.2</v>
@@ -3875,14 +3875,14 @@
       <c r="V40" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W40" s="11" t="n">
+      <c r="W40" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X40" s="3" t="n">
-        <v>26.9</v>
+      <c r="X40" s="8" t="n">
+        <v>86.90000000000001</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>22.8</v>
+        <v>72</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>101.6</v>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>965.6</v>
+        <v>8985.6</v>
       </c>
       <c r="D41" s="10" t="n">
         <v>31.6</v>
@@ -3937,7 +3937,7 @@
         <v>23</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.2</v>
@@ -3948,29 +3948,29 @@
       <c r="R41" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="S41" s="3" t="n">
-        <v>24.9</v>
+      <c r="S41" s="8" t="n">
+        <v>16.9</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V41" s="11" t="n">
-        <v>46.6</v>
+        <v>2</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="X41" s="11" t="n">
-        <v>9218</v>
+      <c r="X41" s="3" t="n">
+        <v>98</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>90.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>18.9</v>
+        <v>8.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3988,16 +3988,16 @@
       <c r="C42" s="3" t="n">
         <v>836.3</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="10" t="n">
         <v>31.6</v>
       </c>
-      <c r="E42" s="12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F42" s="3" t="n">
+      <c r="E42" s="10" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F42" s="10" t="n">
         <v>25.9</v>
       </c>
-      <c r="G42" s="11" t="n">
+      <c r="G42" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -4006,11 +4006,11 @@
       <c r="I42" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="J42" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K42" s="11" t="n">
-        <v>28.1</v>
+      <c r="J42" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>28.4</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>21.9</v>
@@ -4019,10 +4019,10 @@
         <v>21.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>1899</v>
+        <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
@@ -4042,14 +4042,14 @@
       <c r="U42" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="V42" s="11" t="n">
-        <v>822.9</v>
-      </c>
-      <c r="W42" s="11" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="X42" s="11" t="n">
-        <v>88.2</v>
+      <c r="V42" s="3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>828.2</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>90.59999999999999</v>
@@ -4073,14 +4073,14 @@
       <c r="C43" s="3" t="n">
         <v>372.2</v>
       </c>
-      <c r="D43" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E43" s="3" t="n">
+      <c r="D43" s="10" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E43" s="10" t="n">
         <v>21.3</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>29.1</v>
+      <c r="F43" s="10" t="n">
+        <v>24.7</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>8.699999999999999</v>
@@ -4092,7 +4092,7 @@
         <v>2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>13.7</v>
+        <v>3.7</v>
       </c>
       <c r="K43" s="3" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
         <v>29.1</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>80.40000000000001</v>
@@ -4130,17 +4130,17 @@
       <c r="V43" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="W43" s="11" t="n">
-        <v>41.4</v>
+      <c r="W43" s="3" t="n">
+        <v>24.7</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>198.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4156,22 +4156,22 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E44" s="3" t="n">
+        <v>365.9</v>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E44" s="10" t="n">
         <v>21.3</v>
       </c>
-      <c r="F44" s="3" t="n">
+      <c r="F44" s="10" t="n">
         <v>26.9</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="H44" s="3" t="n">
-        <v>89.40000000000001</v>
+      <c r="H44" s="8" t="n">
+        <v>19.4</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>1.9</v>
@@ -4182,11 +4182,11 @@
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="3" t="n">
-        <v>22.3</v>
+      <c r="L44" s="8" t="n">
+        <v>82.3</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>22.3</v>
+        <v>82.3</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>26.9</v>
@@ -4195,31 +4195,31 @@
         <v>100</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R44" s="11" t="n">
+      <c r="R44" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>30.4</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>162</v>
+        <v>62</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>8.6</v>
+        <v>18.6</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="X44" s="3" t="n">
-        <v>82.8</v>
+      <c r="X44" s="8" t="n">
+        <v>28.2</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>84.40000000000001</v>
@@ -4244,73 +4244,73 @@
         <v>2026.2</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>19165.6</v>
+        <v>1901.6</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1128</v>
+        <v>11298.6</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>2026.1</v>
+        <v>226.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>9.1</v>
+        <v>2.1</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>1114.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>1101</v>
+        <v>11</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>118.4</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>743.1</v>
+        <v>783.6</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>11665.9</v>
+        <v>1166.5</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>128.9</v>
+        <v>123.9</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>1148.8</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>292.8</v>
+        <v>293.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>172.8</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>1469.1</v>
+        <v>149.1</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>174.1</v>
+        <v>121.1</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>1450.8</v>
+        <v>1230</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="V45" s="3" t="n">
         <v>158.1</v>
       </c>
       <c r="W45" s="3" t="n">
+        <v>128.2</v>
+      </c>
+      <c r="X45" s="3" t="n">
         <v>172.2</v>
       </c>
-      <c r="X45" s="3" t="n">
-        <v>84.5</v>
-      </c>
       <c r="Y45" s="3" t="n">
-        <v>900.1</v>
+        <v>503.4</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4329,15 +4329,15 @@
         <v>237.6</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="F46" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="G46" s="11" t="n">
+      <c r="G46" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="H46" s="3" t="n">
@@ -4349,11 +4349,9 @@
       <c r="J46" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" s="11" t="n">
-        <v>11.1</v>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>20</v>
@@ -4362,7 +4360,7 @@
         <v>24.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>0.2</v>
@@ -4377,7 +4375,7 @@
         <v>29</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>22.9</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.4</v>
@@ -4392,10 +4390,10 @@
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>83.8</v>
+        <v>88.8</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>62.5</v>
+        <v>6.2</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_correct_values.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_correct_values.xlsx
@@ -789,13 +789,13 @@
       <c r="J4" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="10" t="n">
         <v>20.1</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -807,7 +807,7 @@
       <c r="P4" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="10" t="n">
         <v>28.7</v>
       </c>
       <c r="R4" s="3" t="n">
@@ -822,10 +822,10 @@
       <c r="U4" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="10" t="n">
         <v>25.2</v>
       </c>
-      <c r="W4" s="3" t="n">
+      <c r="W4" s="10" t="n">
         <v>22.8</v>
       </c>
       <c r="X4" s="3" t="n">
@@ -874,13 +874,13 @@
       <c r="J5" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="10" t="n">
         <v>18.8</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -892,7 +892,7 @@
       <c r="P5" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="10" t="n">
         <v>32.6</v>
       </c>
       <c r="R5" s="3" t="n">
@@ -907,10 +907,10 @@
       <c r="U5" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="10" t="n">
         <v>27.2</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="10" t="n">
         <v>24</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -959,13 +959,13 @@
       <c r="J6" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="10" t="n">
         <v>20</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -977,7 +977,7 @@
       <c r="P6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="10" t="n">
         <v>32.7</v>
       </c>
       <c r="R6" s="3" t="n">
@@ -992,10 +992,10 @@
       <c r="U6" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="10" t="n">
         <v>28.1</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="10" t="n">
         <v>23.7</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1044,13 +1044,13 @@
       <c r="J7" s="3" t="n">
         <v>7.9</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="10" t="n">
         <v>20.1</v>
       </c>
       <c r="N7" s="3" t="n">
@@ -1062,10 +1062,10 @@
       <c r="P7" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="Q7" s="10" t="n">
         <v>34.2</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="12" t="n">
         <v>2.2</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1077,10 +1077,10 @@
       <c r="U7" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="10" t="n">
         <v>29.5</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="10" t="n">
         <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1129,13 +1129,13 @@
       <c r="J8" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="10" t="n">
         <v>30.9</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="10" t="n">
         <v>20.6</v>
       </c>
       <c r="N8" s="3" t="n">
@@ -1147,7 +1147,7 @@
       <c r="P8" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="10" t="n">
         <v>21.4</v>
       </c>
       <c r="R8" s="3" t="n">
@@ -1162,10 +1162,10 @@
       <c r="U8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="10" t="n">
         <v>22.2</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="10" t="n">
         <v>21.9</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1214,13 +1214,13 @@
       <c r="J9" s="3" t="n">
         <v>27.5</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="10" t="n">
         <v>30.9</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="10" t="n">
         <v>100.2</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="10" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1232,10 +1232,10 @@
       <c r="P9" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="10" t="n">
         <v>149.6</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="9" t="n">
         <v>121.9</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1247,10 +1247,10 @@
       <c r="U9" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="9" t="n">
         <v>132.8</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="10" t="n">
         <v>116.8</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1302,10 +1302,10 @@
       <c r="K10" s="3" t="n">
         <v>11.1</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="10" t="n">
         <v>19.9</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1317,10 +1317,10 @@
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="8" t="n">
+      <c r="Q10" s="10" t="n">
         <v>29.9</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="9" t="n">
         <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1332,10 +1332,10 @@
       <c r="U10" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="10" t="n">
         <v>23.4</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1387,10 +1387,10 @@
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="10" t="n">
         <v>21.2</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="10" t="n">
         <v>20.9</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1420,7 +1420,7 @@
       <c r="V11" s="3" t="n">
         <v>27.1</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="12" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1472,10 +1472,10 @@
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="10" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="10" t="n">
         <v>23</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1557,10 +1557,10 @@
       <c r="K13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="10" t="n">
         <v>22.1</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="10" t="n">
         <v>21.9</v>
       </c>
       <c r="N13" s="3" t="n">
@@ -1642,10 +1642,10 @@
       <c r="K14" s="3" t="n">
         <v>11.1</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="10" t="n">
         <v>22.4</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="10" t="n">
         <v>22.1</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1657,7 +1657,7 @@
       <c r="P14" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="12" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="R14" s="3" t="n">
@@ -1725,10 +1725,10 @@
       <c r="K15" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="10" t="n">
         <v>21.6</v>
       </c>
       <c r="N15" s="3" t="n">
@@ -1807,13 +1807,13 @@
       <c r="J16" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="9" t="n">
         <v>36.8</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="10" t="n">
         <v>110.6</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="9" t="n">
         <v>109.8</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1825,10 +1825,10 @@
       <c r="P16" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="9" t="n">
         <v>148.7</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="9" t="n">
         <v>1221.9</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1840,10 +1840,10 @@
       <c r="U16" s="3" t="n">
         <v>76.59999999999999</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="9" t="n">
         <v>133.7</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="9" t="n">
         <v>120.7</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1895,10 +1895,10 @@
       <c r="K17" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="10" t="n">
         <v>22.1</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="10" t="n">
         <v>21.9</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1910,10 +1910,10 @@
       <c r="P17" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" s="9" t="n">
         <v>24.4</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1925,10 +1925,10 @@
       <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="9" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="9" t="n">
         <v>24.1</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1978,10 +1978,10 @@
       <c r="K18" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" s="10" t="n">
         <v>21.4</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="10" t="n">
         <v>21.1</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -1993,7 +1993,7 @@
       <c r="P18" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q18" s="3" t="n">
+      <c r="Q18" s="10" t="n">
         <v>32.1</v>
       </c>
       <c r="R18" s="3" t="n">
@@ -2008,7 +2008,7 @@
       <c r="U18" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="10" t="n">
         <v>28.5</v>
       </c>
       <c r="W18" s="3" t="n">
@@ -2063,10 +2063,10 @@
       <c r="K19" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="10" t="n">
         <v>22</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2078,7 +2078,7 @@
       <c r="P19" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="Q19" s="8" t="n">
+      <c r="Q19" s="10" t="n">
         <v>29.9</v>
       </c>
       <c r="R19" s="3" t="n">
@@ -2093,7 +2093,7 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="10" t="n">
         <v>24.3</v>
       </c>
       <c r="W19" s="8" t="n">
@@ -2148,10 +2148,10 @@
       <c r="K20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="10" t="n">
         <v>21.4</v>
       </c>
       <c r="N20" s="3" t="n">
@@ -2163,7 +2163,7 @@
       <c r="P20" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" s="10" t="n">
         <v>30.7</v>
       </c>
       <c r="R20" s="3" t="n">
@@ -2178,7 +2178,7 @@
       <c r="U20" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="10" t="n">
         <v>27.3</v>
       </c>
       <c r="W20" s="3" t="n">
@@ -2233,10 +2233,10 @@
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="10" t="n">
         <v>21.5</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2248,7 +2248,7 @@
       <c r="P21" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q21" s="3" t="n">
+      <c r="Q21" s="10" t="n">
         <v>30.6</v>
       </c>
       <c r="R21" s="3" t="n">
@@ -2263,7 +2263,7 @@
       <c r="U21" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="10" t="n">
         <v>27.8</v>
       </c>
       <c r="W21" s="8" t="n">
@@ -2318,10 +2318,10 @@
       <c r="K22" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="L22" s="10" t="n">
         <v>21.3</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="10" t="n">
         <v>21</v>
       </c>
       <c r="N22" s="3" t="n">
@@ -2333,7 +2333,7 @@
       <c r="P22" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" s="10" t="n">
         <v>32.4</v>
       </c>
       <c r="R22" s="3" t="n">
@@ -2348,7 +2348,7 @@
       <c r="U22" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="V22" s="10" t="n">
         <v>26.5</v>
       </c>
       <c r="W22" s="3" t="n">
@@ -2400,13 +2400,13 @@
       <c r="J23" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="9" t="n">
         <v>49.1</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="10" t="n">
         <v>108.2</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="9" t="n">
         <v>1107</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2418,10 +2418,10 @@
       <c r="P23" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="10" t="n">
         <v>155.7</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="9" t="n">
         <v>128.1</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2433,10 +2433,10 @@
       <c r="U23" s="3" t="n">
         <v>79.40000000000001</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="10" t="n">
         <v>134.4</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="9" t="n">
         <v>20.3</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2488,10 +2488,10 @@
       <c r="K24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="10" t="n">
         <v>21.4</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2503,10 +2503,10 @@
       <c r="P24" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="10" t="n">
         <v>31.1</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="9" t="n">
         <v>85.59999999999999</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2518,10 +2518,10 @@
       <c r="U24" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="10" t="n">
         <v>26.9</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="9" t="n">
         <v>24.1</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2576,7 +2576,7 @@
       <c r="L25" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="M25" s="3" t="n">
+      <c r="M25" s="10" t="n">
         <v>22.1</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2588,10 +2588,10 @@
       <c r="P25" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q25" s="3" t="n">
+      <c r="Q25" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="R25" s="3" t="n">
+      <c r="R25" s="10" t="n">
         <v>24.1</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2606,7 +2606,7 @@
       <c r="V25" s="8" t="n">
         <v>14.4</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="W25" s="10" t="n">
         <v>22.8</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2659,7 +2659,7 @@
       <c r="L26" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="10" t="n">
         <v>21.4</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2671,10 +2671,10 @@
       <c r="P26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="10" t="n">
         <v>24.3</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="10" t="n">
         <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2689,7 +2689,7 @@
       <c r="V26" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="W26" s="3" t="n">
+      <c r="W26" s="10" t="n">
         <v>22.8</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2741,10 +2741,10 @@
       <c r="K27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="L27" s="12" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="10" t="n">
         <v>20.5</v>
       </c>
       <c r="N27" s="3" t="n">
@@ -2756,10 +2756,10 @@
       <c r="P27" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" s="10" t="n">
         <v>28.8</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="10" t="n">
         <v>24.9</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2771,10 +2771,10 @@
       <c r="U27" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="V27" s="8" t="n">
-        <v>826.9</v>
-      </c>
-      <c r="W27" s="3" t="n">
+      <c r="V27" s="12" t="n">
+        <v>82.69</v>
+      </c>
+      <c r="W27" s="10" t="n">
         <v>24.4</v>
       </c>
       <c r="X27" s="8" t="n">
@@ -2829,7 +2829,7 @@
       <c r="L28" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="M28" s="3" t="n">
+      <c r="M28" s="10" t="n">
         <v>20.6</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2841,10 +2841,10 @@
       <c r="P28" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" s="10" t="n">
         <v>31.2</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="R28" s="10" t="n">
         <v>24.8</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2859,7 +2859,7 @@
       <c r="V28" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="W28" s="3" t="n">
+      <c r="W28" s="10" t="n">
         <v>24.6</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2914,7 +2914,7 @@
       <c r="L29" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="10" t="n">
         <v>20.6</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2926,10 +2926,10 @@
       <c r="P29" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" s="10" t="n">
         <v>25.3</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" s="10" t="n">
         <v>23.6</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2944,7 +2944,7 @@
       <c r="V29" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="W29" s="3" t="n">
+      <c r="W29" s="10" t="n">
         <v>21.3</v>
       </c>
       <c r="X29" s="8" t="n">
@@ -2993,13 +2993,13 @@
       <c r="J30" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="9" t="n">
         <v>328.8</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="9" t="n">
         <v>106.5</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="10" t="n">
         <v>105.2</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3011,10 +3011,10 @@
       <c r="P30" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="9" t="n">
         <v>1135.8</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="10" t="n">
         <v>120.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3024,10 +3024,10 @@
         <v>396.8</v>
       </c>
       <c r="U30" s="3" t="inlineStr"/>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="9" t="n">
         <v>126.1</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="10" t="n">
         <v>115.9</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3079,10 +3079,10 @@
       <c r="K31" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="L31" s="3" t="n">
+      <c r="L31" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="10" t="n">
         <v>21</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3094,10 +3094,10 @@
       <c r="P31" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="10" t="n">
         <v>27.2</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="10" t="n">
         <v>24.1</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3109,10 +3109,10 @@
       <c r="U31" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="V31" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="10" t="n">
         <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3164,10 +3164,10 @@
       <c r="K32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="L32" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="M32" s="3" t="n">
+      <c r="M32" s="10" t="n">
         <v>20.1</v>
       </c>
       <c r="N32" s="3" t="n">
@@ -3179,7 +3179,7 @@
       <c r="P32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" s="3" t="n">
+      <c r="Q32" s="10" t="n">
         <v>31.1</v>
       </c>
       <c r="R32" s="3" t="n">
@@ -3197,7 +3197,7 @@
       <c r="V32" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="12" t="n">
         <v>83.8</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3249,10 +3249,10 @@
       <c r="K33" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="10" t="n">
         <v>21.5</v>
       </c>
-      <c r="M33" s="3" t="n">
+      <c r="M33" s="10" t="n">
         <v>21.4</v>
       </c>
       <c r="N33" s="3" t="n">
@@ -3264,7 +3264,7 @@
       <c r="P33" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="10" t="n">
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
@@ -3334,10 +3334,10 @@
       <c r="K34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="10" t="n">
         <v>21.8</v>
       </c>
-      <c r="M34" s="3" t="n">
+      <c r="M34" s="10" t="n">
         <v>21.7</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3349,7 +3349,7 @@
       <c r="P34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="10" t="n">
         <v>30.5</v>
       </c>
       <c r="R34" s="3" t="n">
@@ -3419,10 +3419,10 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M35" s="3" t="n">
+      <c r="M35" s="10" t="n">
         <v>21.3</v>
       </c>
       <c r="N35" s="3" t="n">
@@ -3434,10 +3434,10 @@
       <c r="P35" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q35" s="3" t="n">
+      <c r="Q35" s="10" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="8" t="n">
+      <c r="R35" s="12" t="n">
         <v>46.9</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3504,10 +3504,10 @@
       <c r="K36" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="M36" s="3" t="n">
+      <c r="M36" s="10" t="n">
         <v>20.7</v>
       </c>
       <c r="N36" s="3" t="n">
@@ -3519,7 +3519,7 @@
       <c r="P36" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q36" s="3" t="n">
+      <c r="Q36" s="10" t="n">
         <v>32.1</v>
       </c>
       <c r="R36" s="3" t="n">
@@ -3537,7 +3537,7 @@
       <c r="V36" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="8" t="n">
+      <c r="W36" s="12" t="n">
         <v>46.6</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3586,13 +3586,13 @@
       <c r="J37" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="9" t="n">
         <v>35.6</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="9" t="n">
         <v>1106</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="9" t="n">
         <v>103.2</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3604,10 +3604,10 @@
       <c r="P37" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="10" t="n">
         <v>153.7</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="9" t="n">
         <v>126.2</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3619,10 +3619,10 @@
       <c r="U37" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="9" t="n">
         <v>136.8</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="9" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3672,10 +3672,10 @@
         <v>3.6</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="10" t="n">
         <v>21.2</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="10" t="n">
         <v>21</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3687,10 +3687,10 @@
       <c r="P38" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" s="10" t="n">
         <v>30.7</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="9" t="n">
         <v>25.2</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3702,10 +3702,10 @@
       <c r="U38" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3772,10 +3772,10 @@
       <c r="P39" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="12" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="10" t="n">
         <v>26</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3790,7 +3790,7 @@
       <c r="V39" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="W39" s="3" t="n">
+      <c r="W39" s="10" t="n">
         <v>23.2</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3860,7 +3860,7 @@
       <c r="Q40" s="3" t="n">
         <v>32.8</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="10" t="n">
         <v>26</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3875,7 +3875,7 @@
       <c r="V40" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W40" s="3" t="n">
+      <c r="W40" s="10" t="n">
         <v>23.8</v>
       </c>
       <c r="X40" s="8" t="n">
@@ -3945,7 +3945,7 @@
       <c r="Q41" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="10" t="n">
         <v>21.4</v>
       </c>
       <c r="S41" s="8" t="n">
@@ -3960,7 +3960,7 @@
       <c r="V41" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="W41" s="3" t="n">
+      <c r="W41" s="10" t="n">
         <v>23.4</v>
       </c>
       <c r="X41" s="3" t="n">
@@ -4030,7 +4030,7 @@
       <c r="Q42" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="10" t="n">
         <v>23.8</v>
       </c>
       <c r="S42" s="3" t="n">
@@ -4045,7 +4045,7 @@
       <c r="V42" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="10" t="n">
         <v>22.5</v>
       </c>
       <c r="X42" s="8" t="n">
@@ -4115,7 +4115,7 @@
       <c r="Q43" s="3" t="n">
         <v>29.1</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="10" t="n">
         <v>25.5</v>
       </c>
       <c r="S43" s="3" t="n">
@@ -4130,7 +4130,7 @@
       <c r="V43" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="W43" s="3" t="n">
+      <c r="W43" s="10" t="n">
         <v>24.7</v>
       </c>
       <c r="X43" s="3" t="n">
@@ -4182,10 +4182,10 @@
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="8" t="n">
+      <c r="L44" s="12" t="n">
         <v>82.3</v>
       </c>
-      <c r="M44" s="3" t="n">
+      <c r="M44" s="12" t="n">
         <v>82.3</v>
       </c>
       <c r="N44" s="3" t="n">
@@ -4200,7 +4200,7 @@
       <c r="Q44" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R44" s="3" t="n">
+      <c r="R44" s="10" t="n">
         <v>26.4</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4215,7 +4215,7 @@
       <c r="V44" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="W44" s="3" t="n">
+      <c r="W44" s="10" t="n">
         <v>26.3</v>
       </c>
       <c r="X44" s="8" t="n">
@@ -4264,13 +4264,13 @@
       <c r="J45" s="3" t="n">
         <v>118.4</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="9" t="n">
         <v>783.6</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="9" t="n">
         <v>1166.5</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" s="9" t="n">
         <v>123.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4282,10 +4282,10 @@
       <c r="P45" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="9" t="n">
         <v>172.8</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="10" t="n">
         <v>149.1</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4297,10 +4297,10 @@
       <c r="U45" s="3" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="9" t="n">
         <v>158.1</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="9" t="n">
         <v>128.2</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4350,10 +4350,10 @@
         <v>3.1</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="n">
+      <c r="L46" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="9" t="n">
         <v>20</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4365,10 +4365,10 @@
       <c r="P46" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" s="9" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="3" t="n">
+      <c r="R46" s="9" t="n">
         <v>21.8</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4380,10 +4380,10 @@
       <c r="U46" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="9" t="n">
         <v>26.3</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="10" t="n">
         <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_correct_values.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_correct_values.xlsx
@@ -41,6 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
@@ -49,12 +55,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -143,16 +143,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -766,36 +769,36 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>186.2</v>
-      </c>
-      <c r="D4" s="10" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="D4" s="11" t="n">
         <v>28.6</v>
       </c>
-      <c r="E4" s="10" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>24.1</v>
+      <c r="E4" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>24.4</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>18.2</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>88.2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>11.8</v>
+        <v>1.7</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="10" t="n">
+      <c r="K4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" s="11" t="n">
         <v>20.2</v>
       </c>
-      <c r="M4" s="10" t="n">
+      <c r="M4" s="11" t="n">
         <v>20.1</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -807,7 +810,7 @@
       <c r="P4" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q4" s="10" t="n">
+      <c r="Q4" s="11" t="n">
         <v>28.7</v>
       </c>
       <c r="R4" s="3" t="n">
@@ -822,13 +825,13 @@
       <c r="U4" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="V4" s="10" t="n">
+      <c r="V4" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="W4" s="10" t="n">
+      <c r="W4" s="11" t="n">
         <v>22.8</v>
       </c>
-      <c r="X4" s="3" t="n">
+      <c r="X4" s="8" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
@@ -851,22 +854,22 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>403.8</v>
-      </c>
-      <c r="D5" s="10" t="n">
+        <v>240.3</v>
+      </c>
+      <c r="D5" s="11" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="11" t="n">
         <v>18.2</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="11" t="n">
         <v>25.4</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>16.8</v>
+      <c r="H5" s="8" t="n">
+        <v>416.8</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>3.5</v>
@@ -874,13 +877,13 @@
       <c r="J5" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K5" s="10" t="n">
+      <c r="K5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="10" t="n">
+      <c r="L5" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="M5" s="10" t="n">
+      <c r="M5" s="11" t="n">
         <v>18.8</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -892,7 +895,7 @@
       <c r="P5" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q5" s="10" t="n">
+      <c r="Q5" s="11" t="n">
         <v>32.6</v>
       </c>
       <c r="R5" s="3" t="n">
@@ -907,17 +910,17 @@
       <c r="U5" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="V5" s="10" t="n">
+      <c r="V5" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="W5" s="10" t="n">
+      <c r="W5" s="11" t="n">
         <v>24</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>7174</v>
+        <v>77</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>8.199999999999999</v>
@@ -938,34 +941,34 @@
       <c r="C6" s="3" t="n">
         <v>422.3</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="11" t="n">
         <v>34.2</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="11" t="n">
         <v>18.8</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="11" t="n">
         <v>26.5</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="H6" s="8" t="n">
-        <v>15.2</v>
+      <c r="H6" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="K6" s="10" t="n">
+      <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="10" t="n">
+      <c r="L6" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="M6" s="10" t="n">
+      <c r="M6" s="11" t="n">
         <v>20</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -977,7 +980,7 @@
       <c r="P6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="10" t="n">
+      <c r="Q6" s="11" t="n">
         <v>32.7</v>
       </c>
       <c r="R6" s="3" t="n">
@@ -987,15 +990,15 @@
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>92.8</v>
+        <v>155.8</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="V6" s="10" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="W6" s="10" t="n">
+      <c r="V6" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="W6" s="11" t="n">
         <v>23.7</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1023,14 +1026,14 @@
       <c r="C7" s="3" t="n">
         <v>472.5</v>
       </c>
-      <c r="D7" s="10" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E7" s="10" t="n">
+      <c r="D7" s="11" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E7" s="11" t="n">
         <v>19.3</v>
       </c>
-      <c r="F7" s="10" t="n">
-        <v>27</v>
+      <c r="F7" s="11" t="n">
+        <v>22</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>15.4</v>
@@ -1039,52 +1042,52 @@
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>84.7</v>
+        <v>64.7</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>7.9</v>
       </c>
-      <c r="K7" s="10" t="n">
+      <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="10" t="n">
+      <c r="L7" s="11" t="n">
         <v>20.1</v>
       </c>
-      <c r="M7" s="10" t="n">
+      <c r="M7" s="11" t="n">
         <v>20.1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>23.5</v>
+        <v>2.3</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>100</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="11" t="n">
         <v>34.2</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>20.6</v>
+        <v>50.6</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="V7" s="10" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="W7" s="10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V7" s="12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W7" s="11" t="n">
         <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>27.3</v>
+        <v>2.7</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>66.2</v>
@@ -1108,46 +1111,46 @@
       <c r="C8" s="3" t="n">
         <v>299</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="11" t="n">
         <v>34.6</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="11" t="n">
         <v>27.6</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>14</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="L8" s="10" t="n">
+      <c r="L8" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="M8" s="10" t="n">
+      <c r="M8" s="11" t="n">
         <v>20.6</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>24</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>296.5</v>
+        <v>96.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q8" s="10" t="n">
+      <c r="Q8" s="11" t="n">
         <v>21.4</v>
       </c>
       <c r="R8" s="3" t="n">
@@ -1162,10 +1165,10 @@
       <c r="U8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="V8" s="10" t="n">
+      <c r="V8" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W8" s="10" t="n">
+      <c r="W8" s="11" t="n">
         <v>21.9</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1175,7 +1178,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>20.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1191,16 +1194,16 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1783.2</v>
-      </c>
-      <c r="D9" s="9" t="n">
+        <v>178.3</v>
+      </c>
+      <c r="D9" s="11" t="n">
         <v>164.8</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="11" t="n">
         <v>96.90000000000001</v>
       </c>
-      <c r="F9" s="9" t="n">
-        <v>230.8</v>
+      <c r="F9" s="11" t="n">
+        <v>130.8</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>67.90000000000001</v>
@@ -1209,55 +1212,55 @@
         <v>89.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>27.5</v>
       </c>
-      <c r="K9" s="10" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="L9" s="10" t="n">
+      <c r="K9" s="13" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="L9" s="11" t="n">
         <v>100.2</v>
       </c>
-      <c r="M9" s="10" t="n">
+      <c r="M9" s="11" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>112.8</v>
+        <v>118.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>494.2</v>
+        <v>494.5</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q9" s="10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q9" s="11" t="n">
         <v>149.6</v>
       </c>
-      <c r="R9" s="9" t="n">
+      <c r="R9" s="13" t="n">
         <v>121.9</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>135.7</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>329.9</v>
+        <v>2329.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="V9" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="V9" s="13" t="n">
         <v>132.8</v>
       </c>
-      <c r="W9" s="10" t="n">
+      <c r="W9" s="11" t="n">
         <v>116.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>133.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>3788.8</v>
+        <v>388.8</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>41.6</v>
@@ -1276,16 +1279,16 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="D10" s="10" t="n">
+        <v>356.7</v>
+      </c>
+      <c r="D10" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="11" t="n">
         <v>19.4</v>
       </c>
-      <c r="F10" s="10" t="n">
-        <v>26.4</v>
+      <c r="F10" s="11" t="n">
+        <v>26.2</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>13.6</v>
@@ -1299,13 +1302,11 @@
       <c r="J10" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K10" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L10" s="10" t="n">
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M10" s="11" t="n">
         <v>19.9</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1317,10 +1318,10 @@
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="10" t="n">
+      <c r="Q10" s="11" t="n">
         <v>29.9</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" s="13" t="n">
         <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1332,17 +1333,17 @@
       <c r="U10" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="V10" s="10" t="n">
+      <c r="V10" s="13" t="n">
         <v>26.6</v>
       </c>
-      <c r="W10" s="10" t="n">
+      <c r="W10" s="11" t="n">
         <v>23.4</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>72.8</v>
+        <v>77.8</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>8.300000000000001</v>
@@ -1363,13 +1364,13 @@
       <c r="C11" s="3" t="n">
         <v>265.6</v>
       </c>
-      <c r="D11" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F11" s="10" t="n">
+      <c r="D11" s="11" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F11" s="11" t="n">
         <v>24.9</v>
       </c>
       <c r="G11" s="3" t="n">
@@ -1379,34 +1380,34 @@
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.6</v>
+        <v>11.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="10" t="n">
+      <c r="L11" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M11" s="10" t="n">
+      <c r="M11" s="11" t="n">
         <v>20.9</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>21.3</v>
+        <v>97.3</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q11" s="3" t="n">
+      <c r="Q11" s="11" t="n">
         <v>29.9</v>
       </c>
-      <c r="R11" s="3" t="n">
-        <v>23.5</v>
+      <c r="R11" s="11" t="n">
+        <v>25.5</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>29.8</v>
@@ -1417,20 +1418,20 @@
       <c r="U11" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="V11" s="11" t="n">
         <v>27.1</v>
       </c>
-      <c r="W11" s="12" t="n">
-        <v>94.90000000000001</v>
+      <c r="W11" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>894</v>
+        <v>84</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>5.8</v>
+        <v>159.8</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1446,15 +1447,15 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>242.1</v>
-      </c>
-      <c r="D12" s="12" t="n">
+        <v>347.1</v>
+      </c>
+      <c r="D12" s="11" t="n">
         <v>31.8</v>
       </c>
-      <c r="E12" s="12" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="F12" s="10" t="n">
+      <c r="E12" s="11" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>27.2</v>
       </c>
       <c r="G12" s="3" t="n">
@@ -1467,43 +1468,43 @@
         <v>2.7</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="K12" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="10" t="n">
+      <c r="L12" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="10" t="n">
+      <c r="M12" s="11" t="n">
         <v>23</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>927.5</v>
+        <v>27.5</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="11" t="n">
         <v>31.8</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" s="11" t="n">
         <v>24.9</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>59.8</v>
+        <v>58.8</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="V12" s="3" t="n">
-        <v>21.9</v>
+      <c r="V12" s="11" t="n">
+        <v>27.9</v>
       </c>
       <c r="W12" s="3" t="n">
         <v>24.6</v>
@@ -1515,7 +1516,7 @@
         <v>76.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>81.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1533,13 +1534,13 @@
       <c r="C13" s="3" t="n">
         <v>428.6</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="11" t="n">
         <v>32.8</v>
       </c>
-      <c r="E13" s="10" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F13" s="10" t="n">
+      <c r="E13" s="11" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F13" s="11" t="n">
         <v>26.6</v>
       </c>
       <c r="G13" s="3" t="n">
@@ -1552,15 +1553,15 @@
         <v>3.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="K13" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="10" t="n">
+      <c r="L13" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="M13" s="10" t="n">
+      <c r="M13" s="11" t="n">
         <v>21.9</v>
       </c>
       <c r="N13" s="3" t="n">
@@ -1572,10 +1573,10 @@
       <c r="P13" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="11" t="n">
         <v>32.6</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="11" t="n">
         <v>24.6</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1587,11 +1588,11 @@
       <c r="U13" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="W13" s="3" t="n">
-        <v>24.8</v>
+      <c r="W13" s="12" t="n">
+        <v>2.4</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>29.3</v>
@@ -1600,7 +1601,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>18.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1618,13 +1619,13 @@
       <c r="C14" s="3" t="n">
         <v>190.3</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="11" t="n">
         <v>30.7</v>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E14" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="11" t="n">
         <v>26.3</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -1634,18 +1635,18 @@
         <v>20.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="K14" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K14" s="11" t="n">
         <v>11.1</v>
       </c>
-      <c r="L14" s="10" t="n">
+      <c r="L14" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="M14" s="10" t="n">
+      <c r="M14" s="11" t="n">
         <v>22.1</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1657,14 +1658,14 @@
       <c r="P14" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q14" s="12" t="n">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="R14" s="3" t="n">
+      <c r="Q14" s="11" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R14" s="11" t="n">
         <v>21.1</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>24.2</v>
+        <v>202.1</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>89</v>
@@ -1672,7 +1673,7 @@
       <c r="U14" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" s="11" t="n">
         <v>22</v>
       </c>
       <c r="W14" s="3" t="n">
@@ -1684,7 +1685,9 @@
       <c r="Y14" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="Z14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1701,14 +1704,14 @@
       <c r="C15" s="3" t="n">
         <v>359.6</v>
       </c>
-      <c r="D15" s="10" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>26.6</v>
+      <c r="D15" s="11" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>26.7</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>11.7</v>
@@ -1722,28 +1725,28 @@
       <c r="J15" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K15" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="L15" s="10" t="n">
+      <c r="K15" s="11" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="M15" s="11" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" s="10" t="n">
-        <v>21.6</v>
-      </c>
       <c r="N15" s="3" t="n">
-        <v>25.8</v>
+        <v>29.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>100.2</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="R15" s="3" t="n">
+      <c r="R15" s="11" t="n">
         <v>25.8</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1755,7 +1758,7 @@
       <c r="U15" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="11" t="n">
         <v>28.7</v>
       </c>
       <c r="W15" s="3" t="n">
@@ -1784,19 +1787,19 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1221.2</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>167.9</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>1255.1</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>131.9</v>
+        <v>1591.2</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>131.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>52.4</v>
+        <v>352.4</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>99.2</v>
@@ -1807,29 +1810,29 @@
       <c r="J16" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="K16" s="9" t="n">
+      <c r="K16" s="11" t="n">
         <v>36.8</v>
       </c>
-      <c r="L16" s="10" t="n">
-        <v>110.6</v>
-      </c>
-      <c r="M16" s="9" t="n">
-        <v>109.8</v>
+      <c r="L16" s="13" t="n">
+        <v>1110.6</v>
+      </c>
+      <c r="M16" s="11" t="n">
+        <v>109.5</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1230.7</v>
+        <v>130.7</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1490.1</v>
+        <v>2490.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q16" s="9" t="n">
+      <c r="Q16" s="11" t="n">
         <v>148.7</v>
       </c>
-      <c r="R16" s="9" t="n">
-        <v>1221.9</v>
+      <c r="R16" s="11" t="n">
+        <v>121.9</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>1136.1</v>
@@ -1840,17 +1843,17 @@
       <c r="U16" s="3" t="n">
         <v>76.59999999999999</v>
       </c>
-      <c r="V16" s="9" t="n">
+      <c r="V16" s="11" t="n">
         <v>133.7</v>
       </c>
-      <c r="W16" s="9" t="n">
-        <v>120.7</v>
+      <c r="W16" s="13" t="n">
+        <v>2120.7</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>142.5</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1407.6</v>
+        <v>407.4</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>34.4</v>
@@ -1871,14 +1874,14 @@
       <c r="C17" s="3" t="n">
         <v>318.2</v>
       </c>
-      <c r="D17" s="10" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>26.4</v>
+      <c r="D17" s="11" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>26.3</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>10.5</v>
@@ -1892,43 +1895,43 @@
       <c r="J17" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K17" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="L17" s="10" t="n">
+      <c r="K17" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L17" s="13" t="n">
         <v>22.1</v>
       </c>
-      <c r="M17" s="10" t="n">
+      <c r="M17" s="11" t="n">
         <v>21.9</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>928</v>
+        <v>298</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q17" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q17" s="11" t="n">
         <v>29.7</v>
       </c>
-      <c r="R17" s="9" t="n">
+      <c r="R17" s="11" t="n">
         <v>24.4</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>166.4</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="V17" s="9" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W17" s="9" t="n">
+      <c r="V17" s="11" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="W17" s="13" t="n">
         <v>24.1</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1938,7 +1941,7 @@
         <v>81.5</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1956,69 +1959,71 @@
       <c r="C18" s="3" t="n">
         <v>368</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="11" t="n">
         <v>32.1</v>
       </c>
-      <c r="E18" s="10" t="n">
+      <c r="E18" s="11" t="n">
         <v>21.2</v>
       </c>
-      <c r="F18" s="10" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
+      <c r="F18" s="11" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>10.9</v>
+      </c>
       <c r="H18" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>20.4</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="L18" s="10" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="M18" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="M18" s="11" t="n">
         <v>21.1</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>97.3</v>
+        <v>197.3</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q18" s="10" t="n">
+      <c r="Q18" s="11" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="11" t="n">
         <v>25.2</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>27.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="V18" s="10" t="n">
+      <c r="V18" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="W18" s="3" t="n">
+      <c r="W18" s="11" t="n">
         <v>24.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>21.9</v>
+        <v>27.9</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>171.7</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>11</v>
@@ -2039,20 +2044,20 @@
       <c r="C19" s="3" t="n">
         <v>265.6</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="11" t="n">
         <v>30.4</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="11" t="n">
         <v>22.2</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="11" t="n">
         <v>26.3</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H19" s="8" t="n">
-        <v>91.40000000000001</v>
+      <c r="H19" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.6</v>
@@ -2063,10 +2068,10 @@
       <c r="K19" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="L19" s="10" t="n">
+      <c r="L19" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="M19" s="10" t="n">
+      <c r="M19" s="11" t="n">
         <v>22</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2076,12 +2081,12 @@
         <v>97.59999999999999</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q19" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q19" s="11" t="n">
         <v>29.9</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="11" t="n">
         <v>26</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2093,11 +2098,11 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="10" t="n">
+      <c r="V19" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="W19" s="8" t="n">
-        <v>28.9</v>
+      <c r="W19" s="11" t="n">
+        <v>22.9</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>27.1</v>
@@ -2106,7 +2111,7 @@
         <v>89</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2124,17 +2129,17 @@
       <c r="C20" s="3" t="n">
         <v>365.9</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="11" t="n">
         <v>31.4</v>
       </c>
-      <c r="E20" s="8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>28.5</v>
+      <c r="E20" s="11" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>26.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>19.9</v>
+        <v>29.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>20.6</v>
@@ -2143,55 +2148,55 @@
         <v>2.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="10" t="n">
+      <c r="L20" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M20" s="10" t="n">
+      <c r="M20" s="11" t="n">
         <v>21.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>25.4</v>
+        <v>25.1</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q20" s="10" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q20" s="11" t="n">
         <v>30.7</v>
       </c>
-      <c r="R20" s="3" t="n">
+      <c r="R20" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="S20" s="8" t="n">
-        <v>17.5</v>
+      <c r="S20" s="3" t="n">
+        <v>27.5</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>12.3</v>
+        <v>62.3</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="V20" s="10" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>22.8</v>
+      <c r="V20" s="12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W20" s="11" t="n">
+        <v>23.8</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>725</v>
+        <v>85</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>9.1</v>
+        <v>19.1</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2209,13 +2214,13 @@
       <c r="C21" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D21" s="8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="E21" s="3" t="n">
+      <c r="D21" s="11" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E21" s="11" t="n">
         <v>21.2</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" s="11" t="n">
         <v>25.9</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -2233,10 +2238,10 @@
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="10" t="n">
+      <c r="L21" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M21" s="10" t="n">
+      <c r="M21" s="11" t="n">
         <v>21.5</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2248,10 +2253,10 @@
       <c r="P21" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q21" s="10" t="n">
+      <c r="Q21" s="11" t="n">
         <v>30.6</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="11" t="n">
         <v>26.2</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2263,11 +2268,11 @@
       <c r="U21" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V21" s="10" t="n">
+      <c r="V21" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W21" s="8" t="n">
-        <v>26.6</v>
+      <c r="W21" s="11" t="n">
+        <v>24.6</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>28.9</v>
@@ -2292,19 +2297,19 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>399.3</v>
-      </c>
-      <c r="D22" s="10" t="n">
+        <v>2399.3</v>
+      </c>
+      <c r="D22" s="11" t="n">
         <v>32.9</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E22" s="11" t="n">
         <v>21.1</v>
       </c>
-      <c r="F22" s="10" t="n">
+      <c r="F22" s="11" t="n">
         <v>27</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>11.8</v>
+        <v>1.1</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>19.8</v>
@@ -2316,28 +2321,28 @@
         <v>4.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L22" s="10" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="L22" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="M22" s="10" t="n">
+      <c r="M22" s="11" t="n">
         <v>21</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>97.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q22" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q22" s="11" t="n">
         <v>32.4</v>
       </c>
-      <c r="R22" s="3" t="n">
-        <v>29.9</v>
+      <c r="R22" s="11" t="n">
+        <v>25.9</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>89.3</v>
@@ -2348,10 +2353,10 @@
       <c r="U22" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="V22" s="10" t="n">
+      <c r="V22" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="11" t="n">
         <v>24.6</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2361,7 +2366,7 @@
         <v>86</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>144.9</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2379,17 +2384,17 @@
       <c r="C23" s="3" t="n">
         <v>1739.6</v>
       </c>
-      <c r="D23" s="9" t="n">
-        <v>167.5</v>
-      </c>
-      <c r="E23" s="9" t="n">
+      <c r="D23" s="11" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="E23" s="11" t="n">
         <v>107.2</v>
       </c>
-      <c r="F23" s="9" t="n">
-        <v>138.8</v>
+      <c r="F23" s="11" t="n">
+        <v>132.4</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>20.3</v>
+        <v>50.3</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>101.8</v>
@@ -2398,16 +2403,16 @@
         <v>10.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="L23" s="10" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="L23" s="13" t="n">
         <v>108.2</v>
       </c>
-      <c r="M23" s="9" t="n">
-        <v>1107</v>
+      <c r="M23" s="13" t="n">
+        <v>10.7</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>126.8</v>
@@ -2418,26 +2423,26 @@
       <c r="P23" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q23" s="10" t="n">
+      <c r="Q23" s="11" t="n">
         <v>155.7</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="11" t="n">
         <v>128.1</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>146.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>325.1</v>
+        <v>325.7</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="V23" s="10" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="V23" s="13" t="n">
         <v>134.4</v>
       </c>
-      <c r="W23" s="9" t="n">
-        <v>20.3</v>
+      <c r="W23" s="13" t="n">
+        <v>1120.3</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>140.8</v>
@@ -2446,7 +2451,7 @@
         <v>399</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>362.5</v>
+        <v>36.7</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2462,16 +2467,16 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>343.2</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <v>26.4</v>
+        <v>347.9</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>26.5</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>10.1</v>
@@ -2485,13 +2490,11 @@
       <c r="J24" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L24" s="10" t="n">
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="13" t="n">
         <v>21.6</v>
       </c>
-      <c r="M24" s="10" t="n">
+      <c r="M24" s="11" t="n">
         <v>21.4</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2503,14 +2506,14 @@
       <c r="P24" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="Q24" s="10" t="n">
+      <c r="Q24" s="11" t="n">
         <v>31.1</v>
       </c>
-      <c r="R24" s="9" t="n">
-        <v>85.59999999999999</v>
+      <c r="R24" s="11" t="n">
+        <v>25.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>29.4</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>65.09999999999999</v>
@@ -2518,20 +2521,20 @@
       <c r="U24" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="V24" s="10" t="n">
+      <c r="V24" s="13" t="n">
         <v>26.9</v>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" s="11" t="n">
         <v>24.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>23.2</v>
+        <v>22.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>2981.3</v>
+        <v>79.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>7.3</v>
+        <v>17.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2549,13 +2552,13 @@
       <c r="C25" s="3" t="n">
         <v>106.7</v>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="D25" s="11" t="n">
         <v>26.3</v>
       </c>
-      <c r="E25" s="10" t="n">
+      <c r="E25" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="F25" s="10" t="n">
+      <c r="F25" s="11" t="n">
         <v>23.5</v>
       </c>
       <c r="G25" s="3" t="n">
@@ -2570,14 +2573,14 @@
       <c r="J25" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="11" t="n">
         <v>23.7</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="11" t="n">
         <v>22.4</v>
       </c>
-      <c r="M25" s="10" t="n">
-        <v>22.1</v>
+      <c r="M25" s="12" t="n">
+        <v>98.09999999999999</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>26.4</v>
@@ -2588,10 +2591,10 @@
       <c r="P25" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q25" s="10" t="n">
+      <c r="Q25" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="R25" s="10" t="n">
+      <c r="R25" s="11" t="n">
         <v>24.1</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2601,21 +2604,23 @@
         <v>84.40000000000001</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W25" s="10" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="V25" s="11" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="W25" s="11" t="n">
         <v>22.8</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>8781.700000000001</v>
-      </c>
-      <c r="Z25" s="3" t="inlineStr"/>
+        <v>87.7</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2632,13 +2637,13 @@
       <c r="C26" s="3" t="n">
         <v>290</v>
       </c>
-      <c r="D26" s="10" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="F26" s="10" t="n">
+      <c r="D26" s="11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="F26" s="11" t="n">
         <v>23.1</v>
       </c>
       <c r="G26" s="3" t="n">
@@ -2653,13 +2658,13 @@
       <c r="J26" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="L26" s="3" t="n">
+      <c r="K26" s="11" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="L26" s="11" t="n">
         <v>21.4</v>
       </c>
-      <c r="M26" s="10" t="n">
+      <c r="M26" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2671,25 +2676,25 @@
       <c r="P26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" s="10" t="n">
+      <c r="Q26" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="R26" s="10" t="n">
+      <c r="R26" s="11" t="n">
         <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>28</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>192</v>
+        <v>92</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V26" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V26" s="11" t="n">
         <v>23.8</v>
       </c>
-      <c r="W26" s="10" t="n">
+      <c r="W26" s="11" t="n">
         <v>22.8</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2699,7 +2704,7 @@
         <v>91.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>2.4</v>
+        <v>12.4</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2717,17 +2722,17 @@
       <c r="C27" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D27" s="10" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E27" s="10" t="n">
+      <c r="D27" s="11" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E27" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F27" s="11" t="n">
         <v>25.5</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>19.9</v>
+        <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>19.1</v>
@@ -2738,53 +2743,53 @@
       <c r="J27" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="12" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="M27" s="10" t="n">
+      <c r="L27" s="11" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="M27" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>98</v>
+        <v>298</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q27" s="10" t="n">
+      <c r="Q27" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R27" s="10" t="n">
+      <c r="R27" s="11" t="n">
         <v>24.9</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>29</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>23.2</v>
+        <v>73.2</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="V27" s="12" t="n">
-        <v>82.69</v>
-      </c>
-      <c r="W27" s="10" t="n">
+      <c r="V27" s="11" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="W27" s="11" t="n">
         <v>24.4</v>
       </c>
-      <c r="X27" s="8" t="n">
-        <v>89</v>
+      <c r="X27" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>81.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>6.4</v>
+        <v>16.4</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2802,13 +2807,13 @@
       <c r="C28" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D28" s="10" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E28" s="10" t="n">
+      <c r="D28" s="11" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E28" s="11" t="n">
         <v>20.5</v>
       </c>
-      <c r="F28" s="10" t="n">
+      <c r="F28" s="11" t="n">
         <v>26.1</v>
       </c>
       <c r="G28" s="8" t="n">
@@ -2823,32 +2828,32 @@
       <c r="J28" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" s="11" t="n">
         <v>20.9</v>
       </c>
-      <c r="M28" s="10" t="n">
+      <c r="M28" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q28" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q28" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="R28" s="10" t="n">
+      <c r="R28" s="11" t="n">
         <v>24.8</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>27.2</v>
+        <v>2.7</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>60.2</v>
@@ -2856,10 +2861,10 @@
       <c r="U28" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="V28" s="3" t="n">
+      <c r="V28" s="11" t="n">
         <v>28.6</v>
       </c>
-      <c r="W28" s="10" t="n">
+      <c r="W28" s="11" t="n">
         <v>24.6</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2887,20 +2892,20 @@
       <c r="C29" s="3" t="n">
         <v>246.8</v>
       </c>
-      <c r="D29" s="10" t="n">
+      <c r="D29" s="11" t="n">
         <v>31.5</v>
       </c>
-      <c r="E29" s="10" t="n">
+      <c r="E29" s="11" t="n">
         <v>20.5</v>
       </c>
-      <c r="F29" s="10" t="n">
+      <c r="F29" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="G29" s="8" t="n">
+      <c r="G29" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="H29" s="3" t="n">
-        <v>19.2</v>
+      <c r="H29" s="8" t="n">
+        <v>69.2</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1.6</v>
@@ -2908,50 +2913,50 @@
       <c r="J29" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="11" t="n">
         <v>8.4</v>
       </c>
-      <c r="L29" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="M29" s="10" t="n">
+      <c r="L29" s="11" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="M29" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>95.3</v>
+        <v>2.5</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="Q29" s="10" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="R29" s="10" t="n">
+      <c r="Q29" s="12" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="R29" s="11" t="n">
         <v>23.6</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>827</v>
+        <v>27</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="V29" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V29" s="11" t="n">
         <v>22.4</v>
       </c>
-      <c r="W29" s="10" t="n">
+      <c r="W29" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="X29" s="8" t="n">
-        <v>14.6</v>
+      <c r="X29" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>90.8</v>
+        <v>912.1</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>2.5</v>
@@ -2970,15 +2975,15 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>11056.2</v>
-      </c>
-      <c r="D30" s="10" t="n">
+        <v>1056.2</v>
+      </c>
+      <c r="D30" s="11" t="n">
         <v>145.2</v>
       </c>
-      <c r="E30" s="10" t="n">
+      <c r="E30" s="11" t="n">
         <v>103.2</v>
       </c>
-      <c r="F30" s="10" t="n">
+      <c r="F30" s="11" t="n">
         <v>124.2</v>
       </c>
       <c r="G30" s="3" t="n">
@@ -2991,53 +2996,55 @@
         <v>7.1</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="K30" s="9" t="n">
-        <v>328.8</v>
-      </c>
-      <c r="L30" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="K30" s="11" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="L30" s="13" t="n">
         <v>106.5</v>
       </c>
-      <c r="M30" s="10" t="n">
+      <c r="M30" s="13" t="n">
         <v>105.2</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>123.9</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>487.6</v>
+        <v>2487.6</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q30" s="9" t="n">
+      <c r="Q30" s="13" t="n">
         <v>1135.8</v>
       </c>
-      <c r="R30" s="10" t="n">
+      <c r="R30" s="11" t="n">
         <v>120.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>1240.9</v>
+        <v>140.9</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>396.8</v>
       </c>
-      <c r="U30" s="3" t="inlineStr"/>
-      <c r="V30" s="9" t="n">
-        <v>126.1</v>
-      </c>
-      <c r="W30" s="10" t="n">
+      <c r="U30" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="V30" s="13" t="n">
+        <v>1126.1</v>
+      </c>
+      <c r="W30" s="11" t="n">
         <v>115.9</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>135.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>1424.7</v>
+        <v>1428.7</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>85.8</v>
+        <v>25.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3055,13 +3062,13 @@
       <c r="C31" s="3" t="n">
         <v>211.2</v>
       </c>
-      <c r="D31" s="9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="E31" s="12" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="F31" s="10" t="n">
+      <c r="D31" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F31" s="11" t="n">
         <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
@@ -3076,28 +3083,26 @@
       <c r="J31" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L31" s="9" t="n">
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="M31" s="10" t="n">
+      <c r="M31" s="13" t="n">
         <v>21</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>927.5</v>
+        <v>97.5</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q31" s="10" t="n">
+      <c r="Q31" s="13" t="n">
         <v>27.2</v>
       </c>
-      <c r="R31" s="10" t="n">
+      <c r="R31" s="11" t="n">
         <v>24.1</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3107,19 +3112,19 @@
         <v>79.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="V31" s="9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="V31" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="W31" s="10" t="n">
+      <c r="W31" s="11" t="n">
         <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>84.90000000000001</v>
+        <v>24.9</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>5.2</v>
@@ -3140,14 +3145,14 @@
       <c r="C32" s="3" t="n">
         <v>384.7</v>
       </c>
-      <c r="D32" s="10" t="n">
+      <c r="D32" s="11" t="n">
         <v>31.1</v>
       </c>
-      <c r="E32" s="10" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>23.2</v>
+      <c r="E32" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>25.2</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>11.8</v>
@@ -3161,17 +3166,17 @@
       <c r="J32" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="10" t="n">
+      <c r="L32" s="11" t="n">
         <v>20.1</v>
       </c>
-      <c r="M32" s="10" t="n">
+      <c r="M32" s="11" t="n">
         <v>20.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>23.5</v>
+        <v>23.9</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>100</v>
@@ -3179,7 +3184,7 @@
       <c r="P32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" s="10" t="n">
+      <c r="Q32" s="11" t="n">
         <v>31.1</v>
       </c>
       <c r="R32" s="3" t="n">
@@ -3194,20 +3199,20 @@
       <c r="U32" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="V32" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W32" s="12" t="n">
-        <v>83.8</v>
+      <c r="V32" s="11" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>7641.6</v>
+        <v>746.6</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>19.3</v>
+        <v>195.3</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3225,13 +3230,13 @@
       <c r="C33" s="3" t="n">
         <v>213.3</v>
       </c>
-      <c r="D33" s="10" t="n">
+      <c r="D33" s="11" t="n">
         <v>29.2</v>
       </c>
-      <c r="E33" s="10" t="n">
+      <c r="E33" s="11" t="n">
         <v>19.6</v>
       </c>
-      <c r="F33" s="10" t="n">
+      <c r="F33" s="11" t="n">
         <v>24.4</v>
       </c>
       <c r="G33" s="3" t="n">
@@ -3241,22 +3246,22 @@
         <v>18.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="K33" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="L33" s="10" t="n">
+      <c r="K33" s="11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L33" s="11" t="n">
         <v>21.5</v>
       </c>
-      <c r="M33" s="10" t="n">
+      <c r="M33" s="11" t="n">
         <v>21.4</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>23.9</v>
+        <v>25.4</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>99</v>
@@ -3264,11 +3269,11 @@
       <c r="P33" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="10" t="n">
+      <c r="Q33" s="11" t="n">
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>28.6</v>
+        <v>21.6</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.2</v>
@@ -3279,7 +3284,7 @@
       <c r="U33" s="3" t="n">
         <v>11.5</v>
       </c>
-      <c r="V33" s="3" t="n">
+      <c r="V33" s="11" t="n">
         <v>25.6</v>
       </c>
       <c r="W33" s="3" t="n">
@@ -3289,10 +3294,10 @@
         <v>28.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>26.1</v>
+        <v>0.1</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>144.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3310,14 +3315,14 @@
       <c r="C34" s="3" t="n">
         <v>311.6</v>
       </c>
-      <c r="D34" s="10" t="n">
+      <c r="D34" s="11" t="n">
         <v>31.9</v>
       </c>
-      <c r="E34" s="10" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F34" s="10" t="n">
-        <v>26.6</v>
+      <c r="E34" s="11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>26.7</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>10.5</v>
@@ -3329,31 +3334,31 @@
         <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="K34" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K34" s="11" t="n">
         <v>0.2</v>
       </c>
-      <c r="L34" s="10" t="n">
+      <c r="L34" s="11" t="n">
         <v>21.8</v>
       </c>
-      <c r="M34" s="10" t="n">
+      <c r="M34" s="11" t="n">
         <v>21.7</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="10" t="n">
+      <c r="Q34" s="11" t="n">
         <v>30.5</v>
       </c>
-      <c r="R34" s="3" t="n">
-        <v>25.8</v>
+      <c r="R34" s="8" t="n">
+        <v>35.8</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>30.2</v>
@@ -3364,7 +3369,7 @@
       <c r="U34" s="3" t="n">
         <v>13.3</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="V34" s="11" t="n">
         <v>27.3</v>
       </c>
       <c r="W34" s="3" t="n">
@@ -3374,7 +3379,7 @@
         <v>29.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>82.8</v>
+        <v>82</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>16.5</v>
@@ -3393,15 +3398,15 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>353.4</v>
-      </c>
-      <c r="D35" s="10" t="n">
+        <v>353.1</v>
+      </c>
+      <c r="D35" s="11" t="n">
         <v>31.1</v>
       </c>
-      <c r="E35" s="10" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="F35" s="10" t="n">
+      <c r="E35" s="11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F35" s="11" t="n">
         <v>25.9</v>
       </c>
       <c r="G35" s="3" t="n">
@@ -3416,32 +3421,32 @@
       <c r="J35" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="10" t="n">
+      <c r="L35" s="11" t="n">
         <v>21.6</v>
       </c>
-      <c r="M35" s="10" t="n">
+      <c r="M35" s="11" t="n">
         <v>21.3</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>97.2</v>
+        <v>297.2</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q35" s="10" t="n">
+      <c r="Q35" s="11" t="n">
         <v>31.1</v>
       </c>
       <c r="R35" s="12" t="n">
         <v>46.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>21.8</v>
+        <v>27.8</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>61.3</v>
@@ -3449,7 +3454,7 @@
       <c r="U35" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="V35" s="11" t="n">
         <v>27.8</v>
       </c>
       <c r="W35" s="8" t="n">
@@ -3459,7 +3464,7 @@
         <v>28.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>3.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8.4</v>
@@ -3480,16 +3485,16 @@
       <c r="C36" s="3" t="n">
         <v>430.7</v>
       </c>
-      <c r="D36" s="10" t="n">
+      <c r="D36" s="11" t="n">
         <v>32.1</v>
       </c>
-      <c r="E36" s="10" t="n">
+      <c r="E36" s="11" t="n">
         <v>20.9</v>
       </c>
-      <c r="F36" s="10" t="n">
+      <c r="F36" s="11" t="n">
         <v>26.5</v>
       </c>
-      <c r="G36" s="8" t="n">
+      <c r="G36" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3501,25 +3506,25 @@
       <c r="J36" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="11" t="n">
         <v>30.6</v>
       </c>
-      <c r="L36" s="10" t="n">
+      <c r="L36" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="M36" s="10" t="n">
+      <c r="M36" s="11" t="n">
         <v>20.7</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>97.5</v>
+        <v>925.1</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q36" s="10" t="n">
+      <c r="Q36" s="11" t="n">
         <v>32.1</v>
       </c>
       <c r="R36" s="3" t="n">
@@ -3534,20 +3539,20 @@
       <c r="U36" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="V36" s="11" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="12" t="n">
-        <v>46.6</v>
+      <c r="W36" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>28.8</v>
+        <v>28.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>72</v>
+        <v>172</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1411</v>
+        <v>111</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3565,13 +3570,13 @@
       <c r="C37" s="3" t="n">
         <v>1693.7</v>
       </c>
-      <c r="D37" s="10" t="n">
+      <c r="D37" s="11" t="n">
         <v>155.4</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="11" t="n">
         <v>102</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="F37" s="11" t="n">
         <v>128.7</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3586,14 +3591,14 @@
       <c r="J37" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="K37" s="9" t="n">
+      <c r="K37" s="11" t="n">
         <v>35.6</v>
       </c>
-      <c r="L37" s="9" t="n">
+      <c r="L37" s="13" t="n">
         <v>1106</v>
       </c>
-      <c r="M37" s="9" t="n">
-        <v>103.2</v>
+      <c r="M37" s="11" t="n">
+        <v>105.2</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>124.1</v>
@@ -3602,37 +3607,37 @@
         <v>492.7</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="Q37" s="10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q37" s="11" t="n">
         <v>153.7</v>
       </c>
-      <c r="R37" s="9" t="n">
+      <c r="R37" s="13" t="n">
         <v>126.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>143.1</v>
+        <v>1143.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>324.8</v>
+        <v>2324.8</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V37" s="9" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="V37" s="11" t="n">
         <v>136.8</v>
       </c>
-      <c r="W37" s="9" t="n">
+      <c r="W37" s="13" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>122.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>3928.2</v>
+        <v>392.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>39.7</v>
+        <v>139.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3650,13 +3655,13 @@
       <c r="C38" s="3" t="n">
         <v>338.7</v>
       </c>
-      <c r="D38" s="10" t="n">
+      <c r="D38" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E38" s="11" t="n">
         <v>20.4</v>
       </c>
-      <c r="F38" s="10" t="n">
+      <c r="F38" s="11" t="n">
         <v>25.7</v>
       </c>
       <c r="G38" s="3" t="n">
@@ -3672,47 +3677,47 @@
         <v>3.6</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="10" t="n">
+      <c r="L38" s="11" t="n">
         <v>21.2</v>
       </c>
-      <c r="M38" s="10" t="n">
+      <c r="M38" s="11" t="n">
         <v>21</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>98.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q38" s="10" t="n">
+      <c r="Q38" s="11" t="n">
         <v>30.7</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" s="13" t="n">
         <v>25.2</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="V38" s="9" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="W38" s="9" t="n">
+      <c r="V38" s="13" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="W38" s="13" t="n">
         <v>24.3</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>88.5</v>
+        <v>28.5</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>78</v>
+        <v>29.1</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>7.9</v>
@@ -3733,19 +3738,19 @@
       <c r="C39" s="3" t="n">
         <v>332.5</v>
       </c>
-      <c r="D39" s="10" t="n">
+      <c r="D39" s="11" t="n">
         <v>31.9</v>
       </c>
-      <c r="E39" s="10" t="n">
+      <c r="E39" s="11" t="n">
         <v>20.2</v>
       </c>
-      <c r="F39" s="10" t="n">
+      <c r="F39" s="11" t="n">
         <v>26.1</v>
       </c>
-      <c r="G39" s="8" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="H39" s="8" t="n">
+      <c r="G39" s="3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3755,12 +3760,12 @@
         <v>3</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L39" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L39" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="11" t="n">
         <v>20.9</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -3772,10 +3777,10 @@
       <c r="P39" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q39" s="12" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="R39" s="10" t="n">
+      <c r="Q39" s="11" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="R39" s="11" t="n">
         <v>26</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3785,22 +3790,22 @@
         <v>163.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>11.3</v>
+        <v>18.3</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="W39" s="10" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="W39" s="11" t="n">
         <v>23.2</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>2.7</v>
+        <v>27.5</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>88.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>23.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3816,15 +3821,15 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>153.7</v>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>33</v>
-      </c>
-      <c r="E40" s="10" t="n">
+        <v>1453.7</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E40" s="11" t="n">
         <v>18.8</v>
       </c>
-      <c r="F40" s="10" t="n">
+      <c r="F40" s="11" t="n">
         <v>25.9</v>
       </c>
       <c r="G40" s="3" t="n">
@@ -3842,10 +3847,10 @@
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L40" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="M40" s="11" t="n">
         <v>19.6</v>
       </c>
       <c r="N40" s="3" t="n">
@@ -3857,10 +3862,10 @@
       <c r="P40" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="11" t="n">
         <v>32.8</v>
       </c>
-      <c r="R40" s="10" t="n">
+      <c r="R40" s="11" t="n">
         <v>26</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3875,17 +3880,17 @@
       <c r="V40" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W40" s="10" t="n">
+      <c r="W40" s="11" t="n">
         <v>23.8</v>
       </c>
-      <c r="X40" s="8" t="n">
-        <v>86.90000000000001</v>
+      <c r="X40" s="3" t="n">
+        <v>26.9</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>72</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>101.6</v>
+        <v>10.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3901,15 +3906,15 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>8985.6</v>
-      </c>
-      <c r="D41" s="10" t="n">
+        <v>265.6</v>
+      </c>
+      <c r="D41" s="11" t="n">
         <v>31.6</v>
       </c>
-      <c r="E41" s="10" t="n">
+      <c r="E41" s="11" t="n">
         <v>19.6</v>
       </c>
-      <c r="F41" s="10" t="n">
+      <c r="F41" s="11" t="n">
         <v>25.6</v>
       </c>
       <c r="G41" s="3" t="n">
@@ -3925,12 +3930,12 @@
         <v>1.6</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L41" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L41" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="11" t="n">
         <v>19.8</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3942,14 +3947,14 @@
       <c r="P41" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="11" t="n">
         <v>22.3</v>
       </c>
-      <c r="R41" s="10" t="n">
+      <c r="R41" s="11" t="n">
         <v>21.4</v>
       </c>
-      <c r="S41" s="8" t="n">
-        <v>16.9</v>
+      <c r="S41" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>92.3</v>
@@ -3957,20 +3962,20 @@
       <c r="U41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V41" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="W41" s="10" t="n">
+      <c r="V41" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W41" s="11" t="n">
         <v>23.4</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>190.5</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3986,15 +3991,15 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>836.3</v>
-      </c>
-      <c r="D42" s="10" t="n">
+        <v>236.3</v>
+      </c>
+      <c r="D42" s="11" t="n">
         <v>31.6</v>
       </c>
-      <c r="E42" s="10" t="n">
+      <c r="E42" s="11" t="n">
         <v>20.3</v>
       </c>
-      <c r="F42" s="10" t="n">
+      <c r="F42" s="11" t="n">
         <v>25.9</v>
       </c>
       <c r="G42" s="3" t="n">
@@ -4006,16 +4011,16 @@
       <c r="I42" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="J42" s="8" t="n">
-        <v>8</v>
+      <c r="J42" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="L42" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="L42" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="M42" s="3" t="n">
+      <c r="M42" s="11" t="n">
         <v>21.8</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -4027,36 +4032,34 @@
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="3" t="n">
+      <c r="Q42" s="11" t="n">
         <v>24.1</v>
       </c>
-      <c r="R42" s="10" t="n">
+      <c r="R42" s="11" t="n">
         <v>23.8</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>29.3</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>97.7</v>
+        <v>97.2</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="W42" s="10" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X42" s="8" t="n">
-        <v>828.2</v>
+        <v>24.7</v>
+      </c>
+      <c r="W42" s="11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>28.2</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="Z42" s="3" t="n">
-        <v>2.9</v>
-      </c>
+      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4073,14 +4076,14 @@
       <c r="C43" s="3" t="n">
         <v>372.2</v>
       </c>
-      <c r="D43" s="10" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="E43" s="10" t="n">
+      <c r="D43" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E43" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="F43" s="10" t="n">
-        <v>24.7</v>
+      <c r="F43" s="11" t="n">
+        <v>25.7</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>8.699999999999999</v>
@@ -4097,10 +4100,10 @@
       <c r="K43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="L43" s="11" t="n">
         <v>21.6</v>
       </c>
-      <c r="M43" s="3" t="n">
+      <c r="M43" s="11" t="n">
         <v>21.5</v>
       </c>
       <c r="N43" s="3" t="n">
@@ -4112,10 +4115,10 @@
       <c r="P43" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q43" s="3" t="n">
+      <c r="Q43" s="11" t="n">
         <v>29.1</v>
       </c>
-      <c r="R43" s="10" t="n">
+      <c r="R43" s="11" t="n">
         <v>25.5</v>
       </c>
       <c r="S43" s="3" t="n">
@@ -4128,13 +4131,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W43" s="10" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="W43" s="11" t="n">
         <v>24.7</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>29.1</v>
+        <v>34.1</v>
       </c>
       <c r="Y43" s="3" t="n">
         <v>78</v>
@@ -4158,35 +4161,35 @@
       <c r="C44" s="3" t="n">
         <v>365.9</v>
       </c>
-      <c r="D44" s="10" t="n">
+      <c r="D44" s="11" t="n">
         <v>32.5</v>
       </c>
-      <c r="E44" s="10" t="n">
+      <c r="E44" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="F44" s="10" t="n">
+      <c r="F44" s="11" t="n">
         <v>26.9</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>19.4</v>
+        <v>49.4</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="12" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="M44" s="12" t="n">
-        <v>82.3</v>
+      <c r="L44" s="11" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="M44" s="11" t="n">
+        <v>22.3</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>26.9</v>
@@ -4197,10 +4200,10 @@
       <c r="P44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" s="3" t="n">
+      <c r="Q44" s="11" t="n">
         <v>32.6</v>
       </c>
-      <c r="R44" s="10" t="n">
+      <c r="R44" s="11" t="n">
         <v>26.4</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4213,16 +4216,16 @@
         <v>18.6</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="W44" s="10" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="W44" s="11" t="n">
         <v>26.3</v>
       </c>
-      <c r="X44" s="8" t="n">
-        <v>28.2</v>
+      <c r="X44" s="3" t="n">
+        <v>32.2</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>184.4</v>
       </c>
       <c r="Z44" s="3" t="n">
         <v>16</v>
@@ -4241,40 +4244,40 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2026.2</v>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>1901.6</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>11298.6</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>226.1</v>
+        <v>202.6</v>
+      </c>
+      <c r="D45" s="13" t="n">
+        <v>190.6</v>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>1121.5</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>156.3</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>2.1</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>1114.2</v>
+        <v>1114.7</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>11</v>
+        <v>101.2</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>118.4</v>
-      </c>
-      <c r="K45" s="9" t="n">
-        <v>783.6</v>
-      </c>
-      <c r="L45" s="9" t="n">
-        <v>1166.5</v>
-      </c>
-      <c r="M45" s="9" t="n">
-        <v>123.9</v>
+        <v>18.4</v>
+      </c>
+      <c r="K45" s="13" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="L45" s="13" t="n">
+        <v>126.3</v>
+      </c>
+      <c r="M45" s="13" t="n">
+        <v>10122.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1148.8</v>
+        <v>1148.7</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>293.8</v>
@@ -4282,35 +4285,35 @@
       <c r="P45" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q45" s="9" t="n">
+      <c r="Q45" s="11" t="n">
         <v>172.8</v>
       </c>
-      <c r="R45" s="10" t="n">
+      <c r="R45" s="11" t="n">
         <v>149.1</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>121.1</v>
+        <v>174.1</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>1230</v>
+        <v>2430</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="V45" s="9" t="n">
+      <c r="V45" s="13" t="n">
         <v>158.1</v>
       </c>
-      <c r="W45" s="9" t="n">
-        <v>128.2</v>
+      <c r="W45" s="11" t="n">
+        <v>144.9</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>172.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>503.4</v>
+        <v>583.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4328,17 +4331,17 @@
       <c r="C46" s="3" t="n">
         <v>237.6</v>
       </c>
-      <c r="D46" s="10" t="n">
+      <c r="D46" s="11" t="n">
         <v>31.7</v>
       </c>
-      <c r="E46" s="10" t="n">
+      <c r="E46" s="11" t="n">
         <v>20.2</v>
       </c>
-      <c r="F46" s="10" t="n">
+      <c r="F46" s="11" t="n">
         <v>26</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>21.5</v>
+        <v>11.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>19.1</v>
@@ -4349,51 +4352,53 @@
       <c r="J46" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="9" t="n">
+      <c r="K46" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L46" s="11" t="n">
         <v>21.1</v>
       </c>
-      <c r="M46" s="9" t="n">
-        <v>20</v>
+      <c r="M46" s="11" t="n">
+        <v>21</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="9" t="n">
+      <c r="Q46" s="11" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="9" t="n">
+      <c r="R46" s="13" t="n">
         <v>21.8</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>29</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>22.9</v>
+        <v>75</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V46" s="9" t="n">
+      <c r="V46" s="13" t="n">
         <v>26.3</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="11" t="n">
         <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>88.8</v>
+        <v>823.9</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_correct_values.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_correct_values.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -35,14 +35,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -53,8 +47,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -143,19 +137,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -769,22 +757,22 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E4" s="11" t="n">
+        <v>186.2</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E4" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F4" s="11" t="n">
-        <v>24.4</v>
+      <c r="F4" s="8" t="n">
+        <v>24.3</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="H4" s="8" t="n">
-        <v>88.2</v>
+      <c r="H4" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>1.7</v>
@@ -792,13 +780,13 @@
       <c r="J4" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L4" s="11" t="n">
+      <c r="K4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="M4" s="11" t="n">
+      <c r="M4" s="8" t="n">
         <v>20.1</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -810,10 +798,10 @@
       <c r="P4" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q4" s="11" t="n">
+      <c r="Q4" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -825,13 +813,13 @@
       <c r="U4" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="W4" s="11" t="n">
+      <c r="W4" s="8" t="n">
         <v>22.8</v>
       </c>
-      <c r="X4" s="8" t="n">
+      <c r="X4" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
@@ -854,22 +842,22 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>240.3</v>
-      </c>
-      <c r="D5" s="11" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="D5" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="8" t="n">
         <v>25.4</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="H5" s="8" t="n">
-        <v>416.8</v>
+      <c r="H5" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>3.5</v>
@@ -877,13 +865,13 @@
       <c r="J5" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="11" t="n">
+      <c r="L5" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="M5" s="11" t="n">
+      <c r="M5" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -895,10 +883,10 @@
       <c r="P5" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q5" s="11" t="n">
+      <c r="Q5" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="8" t="n">
         <v>25.4</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -910,10 +898,10 @@
       <c r="U5" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="W5" s="11" t="n">
+      <c r="W5" s="8" t="n">
         <v>24</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -939,15 +927,15 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>422.3</v>
-      </c>
-      <c r="D6" s="11" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D6" s="8" t="n">
         <v>34.2</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="8" t="n">
         <v>26.5</v>
       </c>
       <c r="G6" s="3" t="n">
@@ -962,13 +950,13 @@
       <c r="J6" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="11" t="n">
+      <c r="L6" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="M6" s="11" t="n">
+      <c r="M6" s="8" t="n">
         <v>20</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -980,25 +968,25 @@
       <c r="P6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="11" t="n">
+      <c r="Q6" s="8" t="n">
         <v>32.7</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="8" t="n">
         <v>25.7</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>155.8</v>
+        <v>55.8</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="W6" s="11" t="n">
+      <c r="W6" s="8" t="n">
         <v>23.7</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1026,14 +1014,14 @@
       <c r="C7" s="3" t="n">
         <v>472.5</v>
       </c>
-      <c r="D7" s="11" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="E7" s="11" t="n">
+      <c r="D7" s="8" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="E7" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="F7" s="11" t="n">
-        <v>22</v>
+      <c r="F7" s="8" t="n">
+        <v>27</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>15.4</v>
@@ -1042,22 +1030,22 @@
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>64.7</v>
+        <v>4.7</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="K7" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="11" t="n">
+      <c r="L7" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="M7" s="11" t="n">
+      <c r="M7" s="8" t="n">
         <v>20.1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>2.3</v>
+        <v>23.5</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>100</v>
@@ -1065,11 +1053,11 @@
       <c r="P7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" s="11" t="n">
+      <c r="Q7" s="8" t="n">
         <v>34.2</v>
       </c>
-      <c r="R7" s="12" t="n">
-        <v>2.5</v>
+      <c r="R7" s="8" t="n">
+        <v>25.5</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>27.1</v>
@@ -1078,16 +1066,16 @@
         <v>50.6</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V7" s="12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="W7" s="11" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="W7" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>2.7</v>
+        <v>27.3</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>66.2</v>
@@ -1111,19 +1099,19 @@
       <c r="C8" s="3" t="n">
         <v>299</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="8" t="n">
         <v>34.6</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="8" t="n">
         <v>27.6</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H8" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I8" s="3" t="n">
@@ -1135,10 +1123,10 @@
       <c r="K8" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="L8" s="11" t="n">
+      <c r="L8" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="M8" s="11" t="n">
+      <c r="M8" s="8" t="n">
         <v>20.6</v>
       </c>
       <c r="N8" s="3" t="n">
@@ -1150,10 +1138,10 @@
       <c r="P8" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q8" s="11" t="n">
+      <c r="Q8" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1165,10 +1153,10 @@
       <c r="U8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="W8" s="11" t="n">
+      <c r="W8" s="8" t="n">
         <v>21.9</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1178,7 +1166,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0.6</v>
+        <v>20.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1196,13 +1184,13 @@
       <c r="C9" s="3" t="n">
         <v>178.3</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="8" t="n">
         <v>164.8</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="8" t="n">
         <v>96.90000000000001</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="8" t="n">
         <v>130.8</v>
       </c>
       <c r="G9" s="3" t="n">
@@ -1217,17 +1205,17 @@
       <c r="J9" s="3" t="n">
         <v>27.5</v>
       </c>
-      <c r="K9" s="13" t="n">
+      <c r="K9" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="L9" s="11" t="n">
+      <c r="L9" s="8" t="n">
         <v>100.2</v>
       </c>
-      <c r="M9" s="11" t="n">
+      <c r="M9" s="8" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>118.8</v>
+        <v>15.8</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>494.5</v>
@@ -1235,25 +1223,25 @@
       <c r="P9" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q9" s="11" t="n">
+      <c r="Q9" s="8" t="n">
         <v>149.6</v>
       </c>
-      <c r="R9" s="13" t="n">
+      <c r="R9" s="8" t="n">
         <v>121.9</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>135.7</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>2329.9</v>
+        <v>329.9</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="V9" s="13" t="n">
+      <c r="V9" s="8" t="n">
         <v>132.8</v>
       </c>
-      <c r="W9" s="11" t="n">
+      <c r="W9" s="8" t="n">
         <v>116.8</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1281,13 +1269,13 @@
       <c r="C10" s="3" t="n">
         <v>356.7</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="8" t="n">
         <v>26.2</v>
       </c>
       <c r="G10" s="3" t="n">
@@ -1303,10 +1291,10 @@
         <v>5.5</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="11" t="n">
+      <c r="L10" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="M10" s="11" t="n">
+      <c r="M10" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1318,10 +1306,10 @@
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="11" t="n">
+      <c r="Q10" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R10" s="13" t="n">
+      <c r="R10" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1333,10 +1321,10 @@
       <c r="U10" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="V10" s="13" t="n">
+      <c r="V10" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="W10" s="11" t="n">
+      <c r="W10" s="8" t="n">
         <v>23.4</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1364,13 +1352,13 @@
       <c r="C11" s="3" t="n">
         <v>265.6</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="G11" s="3" t="n">
@@ -1380,18 +1368,18 @@
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K11" s="11" t="n">
+      <c r="K11" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="M11" s="11" t="n">
+      <c r="M11" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1403,10 +1391,10 @@
       <c r="P11" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q11" s="11" t="n">
+      <c r="Q11" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R11" s="11" t="n">
+      <c r="R11" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="S11" s="3" t="n">
@@ -1418,10 +1406,10 @@
       <c r="U11" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V11" s="11" t="n">
+      <c r="V11" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1431,7 +1419,7 @@
         <v>84</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>159.8</v>
+        <v>5.7</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1449,13 +1437,13 @@
       <c r="C12" s="3" t="n">
         <v>347.1</v>
       </c>
-      <c r="D12" s="11" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E12" s="11" t="n">
+      <c r="D12" s="8" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E12" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="8" t="n">
         <v>27.2</v>
       </c>
       <c r="G12" s="3" t="n">
@@ -1470,43 +1458,43 @@
       <c r="J12" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="K12" s="11" t="n">
+      <c r="K12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="11" t="n">
+      <c r="M12" s="8" t="n">
         <v>23</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>27.5</v>
+        <v>97.5</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q12" s="11" t="n">
+      <c r="Q12" s="8" t="n">
         <v>31.8</v>
       </c>
-      <c r="R12" s="11" t="n">
+      <c r="R12" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>58.8</v>
+        <v>57.8</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="V12" s="11" t="n">
+      <c r="V12" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="W12" s="3" t="n">
+      <c r="W12" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="X12" s="3" t="n">
@@ -1534,13 +1522,13 @@
       <c r="C13" s="3" t="n">
         <v>428.6</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="E13" s="11" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="F13" s="11" t="n">
+      <c r="E13" s="8" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F13" s="8" t="n">
         <v>26.6</v>
       </c>
       <c r="G13" s="3" t="n">
@@ -1555,13 +1543,13 @@
       <c r="J13" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K13" s="11" t="n">
+      <c r="K13" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="M13" s="11" t="n">
+      <c r="M13" s="8" t="n">
         <v>21.9</v>
       </c>
       <c r="N13" s="3" t="n">
@@ -1573,10 +1561,10 @@
       <c r="P13" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q13" s="11" t="n">
+      <c r="Q13" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="R13" s="11" t="n">
+      <c r="R13" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1588,11 +1576,11 @@
       <c r="U13" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="V13" s="11" t="n">
+      <c r="V13" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="W13" s="12" t="n">
-        <v>2.4</v>
+      <c r="W13" s="8" t="n">
+        <v>24.8</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>29.3</v>
@@ -1601,7 +1589,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1619,13 +1607,13 @@
       <c r="C14" s="3" t="n">
         <v>190.3</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="8" t="n">
         <v>26.3</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -1640,13 +1628,13 @@
       <c r="J14" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K14" s="11" t="n">
+      <c r="K14" s="8" t="n">
         <v>11.1</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="M14" s="11" t="n">
+      <c r="M14" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1658,10 +1646,10 @@
       <c r="P14" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q14" s="11" t="n">
+      <c r="Q14" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="R14" s="11" t="n">
+      <c r="R14" s="8" t="n">
         <v>21.1</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1673,10 +1661,10 @@
       <c r="U14" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="V14" s="11" t="n">
+      <c r="V14" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="X14" s="3" t="n">
@@ -1704,16 +1692,16 @@
       <c r="C15" s="3" t="n">
         <v>359.6</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="8" t="n">
         <v>32.5</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="G15" s="3" t="n">
         <v>11.7</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1725,17 +1713,17 @@
       <c r="J15" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K15" s="11" t="n">
+      <c r="K15" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="L15" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="M15" s="11" t="n">
+      <c r="L15" s="8" t="n">
         <v>21.6</v>
       </c>
+      <c r="M15" s="8" t="n">
+        <v>21.6</v>
+      </c>
       <c r="N15" s="3" t="n">
-        <v>29.8</v>
+        <v>25.8</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>100</v>
@@ -1743,10 +1731,10 @@
       <c r="P15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="11" t="n">
+      <c r="Q15" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="R15" s="11" t="n">
+      <c r="R15" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1758,10 +1746,10 @@
       <c r="U15" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="V15" s="11" t="n">
+      <c r="V15" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1789,17 +1777,17 @@
       <c r="C16" s="3" t="n">
         <v>1591.2</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="8" t="n">
         <v>157.9</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="8" t="n">
         <v>105.5</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="8" t="n">
         <v>131.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>352.4</v>
+        <v>52.4</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>99.2</v>
@@ -1810,32 +1798,32 @@
       <c r="J16" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="K16" s="11" t="n">
+      <c r="K16" s="8" t="n">
         <v>36.8</v>
       </c>
-      <c r="L16" s="13" t="n">
-        <v>1110.6</v>
-      </c>
-      <c r="M16" s="11" t="n">
+      <c r="L16" s="8" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="M16" s="8" t="n">
         <v>109.5</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>130.7</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>2490.1</v>
+        <v>490.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q16" s="11" t="n">
+      <c r="Q16" s="8" t="n">
         <v>148.7</v>
       </c>
-      <c r="R16" s="11" t="n">
+      <c r="R16" s="8" t="n">
         <v>121.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1136.1</v>
+        <v>136.1</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>331.8</v>
@@ -1843,11 +1831,11 @@
       <c r="U16" s="3" t="n">
         <v>76.59999999999999</v>
       </c>
-      <c r="V16" s="11" t="n">
+      <c r="V16" s="8" t="n">
         <v>133.7</v>
       </c>
-      <c r="W16" s="13" t="n">
-        <v>2120.7</v>
+      <c r="W16" s="8" t="n">
+        <v>120.7</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>142.5</v>
@@ -1874,13 +1862,13 @@
       <c r="C17" s="3" t="n">
         <v>318.2</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="8" t="n">
         <v>31.6</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="8" t="n">
         <v>26.3</v>
       </c>
       <c r="G17" s="3" t="n">
@@ -1898,40 +1886,40 @@
       <c r="K17" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L17" s="13" t="n">
+      <c r="L17" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="M17" s="11" t="n">
+      <c r="M17" s="8" t="n">
         <v>21.9</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>298</v>
+        <v>98</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q17" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q17" s="8" t="n">
         <v>29.7</v>
       </c>
-      <c r="R17" s="11" t="n">
+      <c r="R17" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>22.2</v>
+        <v>27.2</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>166.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="V17" s="11" t="n">
+      <c r="V17" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="W17" s="13" t="n">
+      <c r="W17" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1959,13 +1947,13 @@
       <c r="C18" s="3" t="n">
         <v>368</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="8" t="n">
         <v>32.1</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="8" t="n">
         <v>26.7</v>
       </c>
       <c r="G18" s="3" t="n">
@@ -1986,22 +1974,22 @@
       <c r="L18" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="M18" s="11" t="n">
+      <c r="M18" s="8" t="n">
         <v>21.1</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>197.3</v>
+        <v>97.3</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q18" s="11" t="n">
+      <c r="Q18" s="8" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="11" t="n">
+      <c r="R18" s="8" t="n">
         <v>25.2</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -2013,17 +2001,17 @@
       <c r="U18" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="8" t="n">
         <v>28.5</v>
       </c>
-      <c r="W18" s="11" t="n">
+      <c r="W18" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>171.7</v>
+        <v>71.7</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>11</v>
@@ -2044,13 +2032,13 @@
       <c r="C19" s="3" t="n">
         <v>265.6</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="8" t="n">
         <v>30.4</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="8" t="n">
         <v>26.3</v>
       </c>
       <c r="G19" s="3" t="n">
@@ -2071,7 +2059,7 @@
       <c r="L19" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="M19" s="11" t="n">
+      <c r="M19" s="8" t="n">
         <v>22</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2083,10 +2071,10 @@
       <c r="P19" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q19" s="11" t="n">
+      <c r="Q19" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R19" s="11" t="n">
+      <c r="R19" s="8" t="n">
         <v>26</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2098,10 +2086,10 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="W19" s="11" t="n">
+      <c r="W19" s="8" t="n">
         <v>22.9</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2111,7 +2099,7 @@
         <v>89</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>12.3</v>
+        <v>3.3</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2129,17 +2117,17 @@
       <c r="C20" s="3" t="n">
         <v>365.9</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="8" t="n">
         <v>26.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>29.9</v>
+        <v>9.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>20.6</v>
@@ -2156,22 +2144,22 @@
       <c r="L20" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M20" s="11" t="n">
+      <c r="M20" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>25.1</v>
+        <v>25.4</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q20" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q20" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="R20" s="11" t="n">
+      <c r="R20" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2183,20 +2171,20 @@
       <c r="U20" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="V20" s="12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="W20" s="11" t="n">
+      <c r="V20" s="8" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="W20" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2214,13 +2202,13 @@
       <c r="C21" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -2241,7 +2229,7 @@
       <c r="L21" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M21" s="11" t="n">
+      <c r="M21" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2253,10 +2241,10 @@
       <c r="P21" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q21" s="11" t="n">
+      <c r="Q21" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R21" s="11" t="n">
+      <c r="R21" s="8" t="n">
         <v>26.2</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2268,17 +2256,17 @@
       <c r="U21" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="W21" s="11" t="n">
+      <c r="W21" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>72.3</v>
+        <v>77.3</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>8.4</v>
@@ -2297,19 +2285,19 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2399.3</v>
-      </c>
-      <c r="D22" s="11" t="n">
+        <v>399.3</v>
+      </c>
+      <c r="D22" s="8" t="n">
         <v>32.9</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F22" s="8" t="n">
         <v>27</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1.1</v>
+        <v>11.8</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>19.8</v>
@@ -2326,26 +2314,26 @@
       <c r="L22" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="M22" s="11" t="n">
+      <c r="M22" s="8" t="n">
         <v>21</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q22" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q22" s="8" t="n">
         <v>32.4</v>
       </c>
-      <c r="R22" s="11" t="n">
+      <c r="R22" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>89.3</v>
+        <v>29.3</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>60.5</v>
@@ -2353,10 +2341,10 @@
       <c r="U22" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" s="8" t="n">
         <v>26.5</v>
       </c>
-      <c r="W22" s="11" t="n">
+      <c r="W22" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2366,7 +2354,7 @@
         <v>86</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2384,13 +2372,13 @@
       <c r="C23" s="3" t="n">
         <v>1739.6</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="8" t="n">
         <v>157.5</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E23" s="8" t="n">
         <v>107.2</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F23" s="8" t="n">
         <v>132.4</v>
       </c>
       <c r="G23" s="3" t="n">
@@ -2405,28 +2393,28 @@
       <c r="J23" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="K23" s="13" t="n">
+      <c r="K23" s="11" t="n">
         <v>19.3</v>
       </c>
-      <c r="L23" s="13" t="n">
+      <c r="L23" s="11" t="n">
         <v>108.2</v>
       </c>
-      <c r="M23" s="13" t="n">
-        <v>10.7</v>
+      <c r="M23" s="8" t="n">
+        <v>107</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>126.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>489.4</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q23" s="11" t="n">
+      <c r="Q23" s="8" t="n">
         <v>155.7</v>
       </c>
-      <c r="R23" s="11" t="n">
+      <c r="R23" s="8" t="n">
         <v>128.1</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2438,11 +2426,11 @@
       <c r="U23" s="3" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="V23" s="13" t="n">
+      <c r="V23" s="8" t="n">
         <v>134.4</v>
       </c>
-      <c r="W23" s="13" t="n">
-        <v>1120.3</v>
+      <c r="W23" s="8" t="n">
+        <v>120.3</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>140.8</v>
@@ -2469,13 +2457,13 @@
       <c r="C24" s="3" t="n">
         <v>347.9</v>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="D24" s="8" t="n">
         <v>31.5</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="8" t="n">
         <v>26.5</v>
       </c>
       <c r="G24" s="3" t="n">
@@ -2491,10 +2479,10 @@
         <v>3.9</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="13" t="n">
+      <c r="L24" s="11" t="n">
         <v>21.6</v>
       </c>
-      <c r="M24" s="11" t="n">
+      <c r="M24" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2504,16 +2492,16 @@
         <v>97.90000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q24" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q24" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R24" s="11" t="n">
+      <c r="R24" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>29.4</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>65.09999999999999</v>
@@ -2521,20 +2509,20 @@
       <c r="U24" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="V24" s="13" t="n">
+      <c r="V24" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="W24" s="11" t="n">
+      <c r="W24" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>22.2</v>
+        <v>28.2</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>17.3</v>
+        <v>7.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2552,13 +2540,13 @@
       <c r="C25" s="3" t="n">
         <v>106.7</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="E25" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="F25" s="11" t="n">
+      <c r="F25" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="G25" s="3" t="n">
@@ -2573,13 +2561,13 @@
       <c r="J25" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="K25" s="11" t="n">
+      <c r="K25" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="L25" s="11" t="n">
+      <c r="L25" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="M25" s="10" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2591,10 +2579,10 @@
       <c r="P25" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q25" s="3" t="n">
+      <c r="Q25" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="R25" s="11" t="n">
+      <c r="R25" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2604,12 +2592,12 @@
         <v>84.40000000000001</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="V25" s="11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="V25" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="W25" s="11" t="n">
+      <c r="W25" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2635,19 +2623,19 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>290</v>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F26" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="F26" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>14.1</v>
+        <v>4.1</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>19.2</v>
@@ -2658,10 +2646,10 @@
       <c r="J26" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="K26" s="11" t="n">
+      <c r="K26" s="8" t="n">
         <v>6.7</v>
       </c>
-      <c r="L26" s="11" t="n">
+      <c r="L26" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="M26" s="3" t="n">
@@ -2676,10 +2664,10 @@
       <c r="P26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="R26" s="11" t="n">
+      <c r="R26" s="8" t="n">
         <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2689,12 +2677,12 @@
         <v>92</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V26" s="11" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="V26" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="W26" s="11" t="n">
+      <c r="W26" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2704,7 +2692,7 @@
         <v>91.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2722,13 +2710,13 @@
       <c r="C27" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D27" s="11" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E27" s="11" t="n">
+      <c r="D27" s="8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E27" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F27" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="G27" s="3" t="n">
@@ -2743,10 +2731,10 @@
       <c r="J27" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K27" s="11" t="n">
+      <c r="K27" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="11" t="n">
+      <c r="L27" s="8" t="n">
         <v>20.7</v>
       </c>
       <c r="M27" s="3" t="n">
@@ -2756,15 +2744,15 @@
         <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>298</v>
+        <v>98</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" s="8" t="n">
         <v>28.8</v>
       </c>
-      <c r="R27" s="11" t="n">
+      <c r="R27" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2776,10 +2764,10 @@
       <c r="U27" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="V27" s="11" t="n">
+      <c r="V27" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="W27" s="11" t="n">
+      <c r="W27" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2789,7 +2777,7 @@
         <v>81.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>16.4</v>
+        <v>6.4</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2807,16 +2795,16 @@
       <c r="C28" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D28" s="11" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E28" s="11" t="n">
+      <c r="D28" s="8" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E28" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="F28" s="11" t="n">
+      <c r="F28" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="G28" s="8" t="n">
+      <c r="G28" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2828,10 +2816,10 @@
       <c r="J28" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K28" s="11" t="n">
+      <c r="K28" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="11" t="n">
+      <c r="L28" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="M28" s="3" t="n">
@@ -2846,14 +2834,14 @@
       <c r="P28" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" s="8" t="n">
         <v>31.2</v>
       </c>
-      <c r="R28" s="11" t="n">
+      <c r="R28" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>2.7</v>
+        <v>27.2</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>60.2</v>
@@ -2861,10 +2849,10 @@
       <c r="U28" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="V28" s="11" t="n">
+      <c r="V28" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="W28" s="11" t="n">
+      <c r="W28" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2892,20 +2880,20 @@
       <c r="C29" s="3" t="n">
         <v>246.8</v>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D29" s="8" t="n">
         <v>31.5</v>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="E29" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="F29" s="11" t="n">
+      <c r="F29" s="8" t="n">
         <v>26</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="H29" s="8" t="n">
-        <v>69.2</v>
+      <c r="H29" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1.6</v>
@@ -2913,11 +2901,11 @@
       <c r="J29" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K29" s="11" t="n">
+      <c r="K29" s="8" t="n">
         <v>8.4</v>
       </c>
-      <c r="L29" s="11" t="n">
-        <v>20.1</v>
+      <c r="L29" s="8" t="n">
+        <v>21.1</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>20.6</v>
@@ -2926,30 +2914,30 @@
         <v>23.9</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>2.5</v>
+        <v>95.3</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="Q29" s="12" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="R29" s="11" t="n">
+      <c r="Q29" s="8" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="R29" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="V29" s="11" t="n">
+      <c r="V29" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="W29" s="11" t="n">
+      <c r="W29" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2977,20 +2965,20 @@
       <c r="C30" s="3" t="n">
         <v>1056.2</v>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="D30" s="8" t="n">
         <v>145.2</v>
       </c>
-      <c r="E30" s="11" t="n">
+      <c r="E30" s="8" t="n">
         <v>103.2</v>
       </c>
-      <c r="F30" s="11" t="n">
+      <c r="F30" s="8" t="n">
         <v>124.2</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>42</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>296.6</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>7.1</v>
@@ -2998,28 +2986,28 @@
       <c r="J30" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="K30" s="11" t="n">
+      <c r="K30" s="8" t="n">
         <v>38.8</v>
       </c>
-      <c r="L30" s="13" t="n">
+      <c r="L30" s="8" t="n">
         <v>106.5</v>
       </c>
-      <c r="M30" s="13" t="n">
+      <c r="M30" s="11" t="n">
         <v>105.2</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>123.9</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>2487.6</v>
+        <v>487.6</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q30" s="13" t="n">
-        <v>1135.8</v>
-      </c>
-      <c r="R30" s="11" t="n">
+      <c r="Q30" s="8" t="n">
+        <v>135.8</v>
+      </c>
+      <c r="R30" s="8" t="n">
         <v>120.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3031,17 +3019,17 @@
       <c r="U30" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="V30" s="13" t="n">
-        <v>1126.1</v>
-      </c>
-      <c r="W30" s="11" t="n">
+      <c r="V30" s="8" t="n">
+        <v>126.1</v>
+      </c>
+      <c r="W30" s="8" t="n">
         <v>115.9</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>135.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>1428.7</v>
+        <v>24.7</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>25.8</v>
@@ -3062,13 +3050,13 @@
       <c r="C31" s="3" t="n">
         <v>211.2</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="F31" s="11" t="n">
+      <c r="F31" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
@@ -3084,10 +3072,10 @@
         <v>2.2</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="11" t="n">
+      <c r="L31" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="M31" s="13" t="n">
+      <c r="M31" s="11" t="n">
         <v>21</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3099,10 +3087,10 @@
       <c r="P31" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q31" s="13" t="n">
+      <c r="Q31" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="R31" s="11" t="n">
+      <c r="R31" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3112,19 +3100,19 @@
         <v>79.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="V31" s="11" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="V31" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="W31" s="11" t="n">
+      <c r="W31" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>24.9</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>5.2</v>
@@ -3145,19 +3133,19 @@
       <c r="C32" s="3" t="n">
         <v>384.7</v>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="D32" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E32" s="11" t="n">
+      <c r="E32" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="F32" s="11" t="n">
+      <c r="F32" s="8" t="n">
         <v>25.2</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="H32" s="8" t="n">
+      <c r="H32" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I32" s="3" t="n">
@@ -3166,17 +3154,17 @@
       <c r="J32" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="K32" s="11" t="n">
+      <c r="K32" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="11" t="n">
+      <c r="L32" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="M32" s="11" t="n">
+      <c r="M32" s="8" t="n">
         <v>20.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>100</v>
@@ -3184,7 +3172,7 @@
       <c r="P32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" s="11" t="n">
+      <c r="Q32" s="8" t="n">
         <v>31.1</v>
       </c>
       <c r="R32" s="3" t="n">
@@ -3199,20 +3187,20 @@
       <c r="U32" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="V32" s="11" t="n">
+      <c r="V32" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>746.6</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>195.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3230,13 +3218,13 @@
       <c r="C33" s="3" t="n">
         <v>213.3</v>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D33" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E33" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="F33" s="11" t="n">
+      <c r="F33" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="G33" s="3" t="n">
@@ -3246,34 +3234,34 @@
         <v>18.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="K33" s="11" t="n">
+      <c r="K33" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="L33" s="11" t="n">
+      <c r="L33" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="M33" s="11" t="n">
+      <c r="M33" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>99</v>
+        <v>99.7</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="11" t="n">
+      <c r="Q33" s="8" t="n">
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>21.6</v>
+        <v>22.6</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.2</v>
@@ -3284,10 +3272,10 @@
       <c r="U33" s="3" t="n">
         <v>11.5</v>
       </c>
-      <c r="V33" s="11" t="n">
+      <c r="V33" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3297,7 +3285,7 @@
         <v>0.1</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3315,13 +3303,13 @@
       <c r="C34" s="3" t="n">
         <v>311.6</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="E34" s="11" t="n">
+      <c r="E34" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="F34" s="11" t="n">
+      <c r="F34" s="8" t="n">
         <v>26.7</v>
       </c>
       <c r="G34" s="3" t="n">
@@ -3336,29 +3324,29 @@
       <c r="J34" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K34" s="11" t="n">
+      <c r="K34" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="L34" s="11" t="n">
+      <c r="L34" s="8" t="n">
         <v>21.8</v>
       </c>
-      <c r="M34" s="11" t="n">
+      <c r="M34" s="8" t="n">
         <v>21.7</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="11" t="n">
+      <c r="Q34" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="R34" s="8" t="n">
-        <v>35.8</v>
+      <c r="R34" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>30.2</v>
@@ -3369,10 +3357,10 @@
       <c r="U34" s="3" t="n">
         <v>13.3</v>
       </c>
-      <c r="V34" s="11" t="n">
+      <c r="V34" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3382,7 +3370,7 @@
         <v>82</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3398,15 +3386,15 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>353.1</v>
-      </c>
-      <c r="D35" s="11" t="n">
+        <v>353.4</v>
+      </c>
+      <c r="D35" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E35" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="F35" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="G35" s="3" t="n">
@@ -3421,32 +3409,32 @@
       <c r="J35" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K35" s="11" t="n">
+      <c r="K35" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="11" t="n">
+      <c r="L35" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M35" s="11" t="n">
+      <c r="M35" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>297.2</v>
+        <v>97.2</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q35" s="11" t="n">
+      <c r="Q35" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="12" t="n">
-        <v>46.9</v>
+      <c r="R35" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>27.8</v>
+        <v>27.5</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>61.3</v>
@@ -3454,17 +3442,17 @@
       <c r="U35" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="V35" s="11" t="n">
+      <c r="V35" s="8" t="n">
         <v>27.8</v>
       </c>
       <c r="W35" s="8" t="n">
-        <v>16.6</v>
+        <v>24.6</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8.4</v>
@@ -3483,15 +3471,15 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>430.7</v>
-      </c>
-      <c r="D36" s="11" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="D36" s="8" t="n">
         <v>32.1</v>
       </c>
-      <c r="E36" s="11" t="n">
+      <c r="E36" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="F36" s="11" t="n">
+      <c r="F36" s="8" t="n">
         <v>26.5</v>
       </c>
       <c r="G36" s="3" t="n">
@@ -3506,13 +3494,13 @@
       <c r="J36" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K36" s="11" t="n">
+      <c r="K36" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="L36" s="11" t="n">
+      <c r="L36" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="M36" s="11" t="n">
+      <c r="M36" s="8" t="n">
         <v>20.7</v>
       </c>
       <c r="N36" s="3" t="n">
@@ -3524,7 +3512,7 @@
       <c r="P36" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q36" s="11" t="n">
+      <c r="Q36" s="8" t="n">
         <v>32.1</v>
       </c>
       <c r="R36" s="3" t="n">
@@ -3539,20 +3527,20 @@
       <c r="U36" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="V36" s="11" t="n">
+      <c r="V36" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>28.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>172</v>
+        <v>72</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3570,13 +3558,13 @@
       <c r="C37" s="3" t="n">
         <v>1693.7</v>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="D37" s="8" t="n">
         <v>155.4</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E37" s="8" t="n">
         <v>102</v>
       </c>
-      <c r="F37" s="11" t="n">
+      <c r="F37" s="8" t="n">
         <v>128.7</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3591,13 +3579,13 @@
       <c r="J37" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="K37" s="11" t="n">
+      <c r="K37" s="8" t="n">
         <v>35.6</v>
       </c>
-      <c r="L37" s="13" t="n">
-        <v>1106</v>
-      </c>
-      <c r="M37" s="11" t="n">
+      <c r="L37" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="M37" s="8" t="n">
         <v>105.2</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3609,35 +3597,35 @@
       <c r="P37" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="Q37" s="11" t="n">
+      <c r="Q37" s="8" t="n">
         <v>153.7</v>
       </c>
-      <c r="R37" s="13" t="n">
+      <c r="R37" s="11" t="n">
         <v>126.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>1143.1</v>
+        <v>143.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>2324.8</v>
+        <v>324.8</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="V37" s="11" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="V37" s="8" t="n">
         <v>136.8</v>
       </c>
-      <c r="W37" s="13" t="n">
+      <c r="W37" s="8" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>122.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>392.2</v>
+        <v>398.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>139.7</v>
+        <v>39.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3655,13 +3643,13 @@
       <c r="C38" s="3" t="n">
         <v>338.7</v>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="D38" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="F38" s="11" t="n">
+      <c r="F38" s="8" t="n">
         <v>25.7</v>
       </c>
       <c r="G38" s="3" t="n">
@@ -3677,25 +3665,25 @@
         <v>3.6</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="11" t="n">
+      <c r="L38" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="M38" s="11" t="n">
+      <c r="M38" s="8" t="n">
         <v>21</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q38" s="11" t="n">
+      <c r="Q38" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="R38" s="13" t="n">
+      <c r="R38" s="11" t="n">
         <v>25.2</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3707,17 +3695,17 @@
       <c r="U38" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="V38" s="13" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="W38" s="13" t="n">
+      <c r="V38" s="8" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="W38" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>29.1</v>
+        <v>78</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>7.9</v>
@@ -3738,13 +3726,13 @@
       <c r="C39" s="3" t="n">
         <v>332.5</v>
       </c>
-      <c r="D39" s="11" t="n">
+      <c r="D39" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="E39" s="11" t="n">
+      <c r="E39" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F39" s="11" t="n">
+      <c r="F39" s="8" t="n">
         <v>26.1</v>
       </c>
       <c r="G39" s="3" t="n">
@@ -3760,12 +3748,12 @@
         <v>3</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L39" s="11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L39" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="M39" s="11" t="n">
+      <c r="M39" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -3777,25 +3765,25 @@
       <c r="P39" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q39" s="11" t="n">
+      <c r="Q39" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="R39" s="11" t="n">
+      <c r="R39" s="8" t="n">
         <v>26</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>163.2</v>
+        <v>63.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>18.3</v>
+        <v>17.3</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="W39" s="11" t="n">
+      <c r="W39" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3805,7 +3793,7 @@
         <v>88.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>23.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3821,15 +3809,15 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1453.7</v>
-      </c>
-      <c r="D40" s="11" t="n">
+        <v>453.7</v>
+      </c>
+      <c r="D40" s="8" t="n">
         <v>32.9</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="E40" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="G40" s="3" t="n">
@@ -3839,7 +3827,7 @@
         <v>18.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.7</v>
+        <v>22.7</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>5</v>
@@ -3847,10 +3835,10 @@
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="11" t="n">
+      <c r="L40" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="M40" s="11" t="n">
+      <c r="M40" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="N40" s="3" t="n">
@@ -3862,10 +3850,10 @@
       <c r="P40" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q40" s="11" t="n">
+      <c r="Q40" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="R40" s="11" t="n">
+      <c r="R40" s="8" t="n">
         <v>26</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3880,7 +3868,7 @@
       <c r="V40" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W40" s="11" t="n">
+      <c r="W40" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3908,13 +3896,13 @@
       <c r="C41" s="3" t="n">
         <v>265.6</v>
       </c>
-      <c r="D41" s="11" t="n">
+      <c r="D41" s="8" t="n">
         <v>31.6</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E41" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="F41" s="11" t="n">
+      <c r="F41" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="G41" s="3" t="n">
@@ -3932,10 +3920,10 @@
       <c r="K41" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="L41" s="11" t="n">
+      <c r="L41" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="M41" s="11" t="n">
+      <c r="M41" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3947,10 +3935,10 @@
       <c r="P41" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q41" s="11" t="n">
+      <c r="Q41" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="R41" s="11" t="n">
+      <c r="R41" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="S41" s="3" t="n">
@@ -3962,17 +3950,17 @@
       <c r="U41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V41" s="8" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="W41" s="11" t="n">
+      <c r="V41" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="W41" s="8" t="n">
         <v>23.4</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>28</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>190.5</v>
+        <v>90.5</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>2.9</v>
@@ -3993,13 +3981,13 @@
       <c r="C42" s="3" t="n">
         <v>236.3</v>
       </c>
-      <c r="D42" s="11" t="n">
+      <c r="D42" s="8" t="n">
         <v>31.6</v>
       </c>
-      <c r="E42" s="11" t="n">
+      <c r="E42" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="F42" s="11" t="n">
+      <c r="F42" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="G42" s="3" t="n">
@@ -4017,40 +4005,40 @@
       <c r="K42" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="L42" s="11" t="n">
+      <c r="L42" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="M42" s="11" t="n">
+      <c r="M42" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>26</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="11" t="n">
+      <c r="Q42" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="R42" s="11" t="n">
+      <c r="R42" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>29.3</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>97.2</v>
+        <v>97.7</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="W42" s="11" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="W42" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="X42" s="3" t="n">
@@ -4076,13 +4064,13 @@
       <c r="C43" s="3" t="n">
         <v>372.2</v>
       </c>
-      <c r="D43" s="11" t="n">
+      <c r="D43" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E43" s="11" t="n">
+      <c r="E43" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="F43" s="11" t="n">
+      <c r="F43" s="8" t="n">
         <v>25.7</v>
       </c>
       <c r="G43" s="3" t="n">
@@ -4100,10 +4088,10 @@
       <c r="K43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="11" t="n">
+      <c r="L43" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M43" s="11" t="n">
+      <c r="M43" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="N43" s="3" t="n">
@@ -4115,14 +4103,14 @@
       <c r="P43" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q43" s="11" t="n">
+      <c r="Q43" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="R43" s="11" t="n">
+      <c r="R43" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>30.4</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>75.59999999999999</v>
@@ -4133,7 +4121,7 @@
       <c r="V43" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W43" s="11" t="n">
+      <c r="W43" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="X43" s="3" t="n">
@@ -4161,34 +4149,34 @@
       <c r="C44" s="3" t="n">
         <v>365.9</v>
       </c>
-      <c r="D44" s="11" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="E44" s="11" t="n">
+      <c r="D44" s="8" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E44" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="F44" s="11" t="n">
+      <c r="F44" s="8" t="n">
         <v>26.9</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="H44" s="8" t="n">
-        <v>49.4</v>
+      <c r="H44" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>8.6</v>
+        <v>3.6</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="11" t="n">
+      <c r="L44" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="M44" s="11" t="n">
+      <c r="M44" s="8" t="n">
         <v>22.3</v>
       </c>
       <c r="N44" s="3" t="n">
@@ -4200,10 +4188,10 @@
       <c r="P44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" s="11" t="n">
+      <c r="Q44" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="R44" s="11" t="n">
+      <c r="R44" s="8" t="n">
         <v>26.4</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4216,19 +4204,19 @@
         <v>18.6</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="W44" s="11" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="W44" s="8" t="n">
         <v>26.3</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>32.2</v>
+        <v>32.8</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>184.4</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4246,71 +4234,71 @@
       <c r="C45" s="3" t="n">
         <v>202.6</v>
       </c>
-      <c r="D45" s="13" t="n">
+      <c r="D45" s="8" t="n">
         <v>190.6</v>
       </c>
-      <c r="E45" s="13" t="n">
-        <v>1121.5</v>
-      </c>
-      <c r="F45" s="13" t="n">
-        <v>156.3</v>
+      <c r="E45" s="8" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>156.1</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>69.09999999999999</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>1114.7</v>
+        <v>114.7</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>101.2</v>
+        <v>10.2</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="K45" s="13" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="L45" s="13" t="n">
-        <v>126.3</v>
-      </c>
-      <c r="M45" s="13" t="n">
-        <v>10122.9</v>
+      <c r="K45" s="11" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="M45" s="8" t="n">
+        <v>125.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1148.7</v>
+        <v>148.7</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>293.8</v>
+        <v>593.8</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q45" s="11" t="n">
+      <c r="Q45" s="8" t="n">
         <v>172.8</v>
       </c>
-      <c r="R45" s="11" t="n">
+      <c r="R45" s="8" t="n">
         <v>149.1</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>174.1</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>2430</v>
+        <v>250</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="V45" s="13" t="n">
+      <c r="V45" s="11" t="n">
         <v>158.1</v>
       </c>
-      <c r="W45" s="11" t="n">
+      <c r="W45" s="8" t="n">
         <v>144.9</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>172.2</v>
+        <v>172.5</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>583.7</v>
+        <v>503.7</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>34</v>
@@ -4329,15 +4317,15 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>237.6</v>
-      </c>
-      <c r="D46" s="11" t="n">
+        <v>337.6</v>
+      </c>
+      <c r="D46" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="E46" s="11" t="n">
+      <c r="E46" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F46" s="11" t="n">
+      <c r="F46" s="8" t="n">
         <v>26</v>
       </c>
       <c r="G46" s="3" t="n">
@@ -4353,12 +4341,12 @@
         <v>3.1</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L46" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L46" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="M46" s="11" t="n">
+      <c r="M46" s="8" t="n">
         <v>21</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4370,11 +4358,11 @@
       <c r="P46" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="11" t="n">
+      <c r="Q46" s="8" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="13" t="n">
-        <v>21.8</v>
+      <c r="R46" s="8" t="n">
+        <v>24.8</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>29</v>
@@ -4385,17 +4373,17 @@
       <c r="U46" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V46" s="13" t="n">
+      <c r="V46" s="11" t="n">
         <v>26.3</v>
       </c>
-      <c r="W46" s="11" t="n">
+      <c r="W46" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>823.9</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>5.7</v>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_correct_values.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_correct_values.xlsx
@@ -119,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -137,13 +137,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -927,7 +924,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>22.3</v>
+        <v>122.3</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>34.2</v>
@@ -1182,7 +1179,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>178.3</v>
+        <v>1783.5</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>164.8</v>
@@ -1215,7 +1212,7 @@
         <v>99.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>15.8</v>
+        <v>115.8</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>494.5</v>
@@ -1251,7 +1248,7 @@
         <v>388.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>41.6</v>
+        <v>22.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1290,7 +1287,9 @@
       <c r="J10" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L10" s="8" t="n">
         <v>20</v>
       </c>
@@ -1438,7 +1437,7 @@
         <v>347.1</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>31.2</v>
+        <v>31.8</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>22.6</v>
@@ -2297,7 +2296,7 @@
         <v>27</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>11.8</v>
+        <v>118.2</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>19.8</v>
@@ -2311,8 +2310,8 @@
       <c r="K22" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="L22" s="3" t="n">
-        <v>21.3</v>
+      <c r="L22" s="10" t="n">
+        <v>22.13</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>21</v>
@@ -2393,10 +2392,10 @@
       <c r="J23" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="K23" s="11" t="n">
+      <c r="K23" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="L23" s="11" t="n">
+      <c r="L23" s="9" t="n">
         <v>108.2</v>
       </c>
       <c r="M23" s="8" t="n">
@@ -2406,7 +2405,7 @@
         <v>126.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>489.4</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>2.2</v>
@@ -2479,7 +2478,7 @@
         <v>3.9</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="11" t="n">
+      <c r="L24" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="M24" s="8" t="n">
@@ -2674,7 +2673,7 @@
         <v>28</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>92</v>
+        <v>28.2</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>22.9</v>
@@ -2744,7 +2743,7 @@
         <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0.4</v>
@@ -2811,7 +2810,7 @@
         <v>18.9</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.8</v>
@@ -2832,7 +2831,7 @@
         <v>97.3</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q28" s="8" t="n">
         <v>31.2</v>
@@ -2992,7 +2991,7 @@
       <c r="L30" s="8" t="n">
         <v>106.5</v>
       </c>
-      <c r="M30" s="11" t="n">
+      <c r="M30" s="9" t="n">
         <v>105.2</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3007,8 +3006,8 @@
       <c r="Q30" s="8" t="n">
         <v>135.8</v>
       </c>
-      <c r="R30" s="8" t="n">
-        <v>120.7</v>
+      <c r="R30" s="9" t="n">
+        <v>1207.2</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>140.9</v>
@@ -3017,7 +3016,7 @@
         <v>396.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="V30" s="8" t="n">
         <v>126.1</v>
@@ -3029,7 +3028,7 @@
         <v>135.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>24.7</v>
+        <v>424.7</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>25.8</v>
@@ -3069,13 +3068,13 @@
         <v>1.4</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="M31" s="11" t="n">
+      <c r="M31" s="9" t="n">
         <v>21</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3100,7 +3099,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="V31" s="8" t="n">
         <v>25.2</v>
@@ -3175,7 +3174,7 @@
       <c r="Q32" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3190,7 +3189,7 @@
       <c r="V32" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="W32" s="8" t="n">
+      <c r="W32" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3252,7 +3251,7 @@
         <v>25.4</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>99.7</v>
+        <v>99</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0.2</v>
@@ -3260,8 +3259,8 @@
       <c r="Q33" s="8" t="n">
         <v>28.9</v>
       </c>
-      <c r="R33" s="3" t="n">
-        <v>22.6</v>
+      <c r="R33" s="8" t="n">
+        <v>24.6</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.2</v>
@@ -3275,7 +3274,7 @@
       <c r="V33" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3345,7 +3344,7 @@
       <c r="Q34" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3360,7 +3359,7 @@
       <c r="V34" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="W34" s="8" t="n">
+      <c r="W34" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3430,7 +3429,7 @@
       <c r="Q35" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3445,14 +3444,14 @@
       <c r="V35" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="W35" s="8" t="n">
-        <v>24.6</v>
+      <c r="W35" s="3" t="n">
+        <v>26.6</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>77.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8.4</v>
@@ -3471,7 +3470,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>30.7</v>
+        <v>430.7</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>32.1</v>
@@ -3515,7 +3514,7 @@
       <c r="Q36" s="8" t="n">
         <v>32.1</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="8" t="n">
         <v>26</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3530,7 +3529,7 @@
       <c r="V36" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="8" t="n">
+      <c r="W36" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3600,7 +3599,7 @@
       <c r="Q37" s="8" t="n">
         <v>153.7</v>
       </c>
-      <c r="R37" s="11" t="n">
+      <c r="R37" s="8" t="n">
         <v>126.2</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3615,14 +3614,14 @@
       <c r="V37" s="8" t="n">
         <v>136.8</v>
       </c>
-      <c r="W37" s="8" t="n">
+      <c r="W37" s="9" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>122.4</v>
+        <v>142.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>398.2</v>
+        <v>392.2</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>39.7</v>
@@ -3683,7 +3682,7 @@
       <c r="Q38" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="R38" s="11" t="n">
+      <c r="R38" s="8" t="n">
         <v>25.2</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3698,14 +3697,14 @@
       <c r="V38" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="W38" s="8" t="n">
+      <c r="W38" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>78</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>7.9</v>
@@ -3730,7 +3729,7 @@
         <v>31.9</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="F39" s="8" t="n">
         <v>26.1</v>
@@ -3748,7 +3747,7 @@
         <v>3</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L39" s="8" t="n">
         <v>21</v>
@@ -3780,7 +3779,7 @@
       <c r="U39" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="W39" s="8" t="n">
@@ -3827,7 +3826,7 @@
         <v>18.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>22.7</v>
+        <v>2.7</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>5</v>
@@ -3865,7 +3864,7 @@
       <c r="U40" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="8" t="n">
         <v>27.8</v>
       </c>
       <c r="W40" s="8" t="n">
@@ -3950,7 +3949,7 @@
       <c r="U41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="W41" s="8" t="n">
@@ -4000,7 +3999,7 @@
         <v>0.7</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>28.7</v>
@@ -4035,8 +4034,8 @@
       <c r="U42" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="V42" s="3" t="n">
-        <v>22.7</v>
+      <c r="V42" s="8" t="n">
+        <v>24.7</v>
       </c>
       <c r="W42" s="8" t="n">
         <v>23.5</v>
@@ -4118,7 +4117,7 @@
       <c r="U43" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V43" s="3" t="n">
+      <c r="V43" s="8" t="n">
         <v>27.8</v>
       </c>
       <c r="W43" s="8" t="n">
@@ -4203,7 +4202,7 @@
       <c r="U44" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="V44" s="3" t="n">
+      <c r="V44" s="8" t="n">
         <v>28.5</v>
       </c>
       <c r="W44" s="8" t="n">
@@ -4232,16 +4231,16 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>202.6</v>
+        <v>2026.2</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>190.6</v>
       </c>
-      <c r="E45" s="8" t="n">
-        <v>121.5</v>
-      </c>
-      <c r="F45" s="8" t="n">
-        <v>156.1</v>
+      <c r="E45" s="9" t="n">
+        <v>1215.2</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>156.3</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>69.09999999999999</v>
@@ -4255,8 +4254,8 @@
       <c r="J45" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="K45" s="11" t="n">
-        <v>72.3</v>
+      <c r="K45" s="9" t="n">
+        <v>78.3</v>
       </c>
       <c r="L45" s="8" t="n">
         <v>126.5</v>
@@ -4283,12 +4282,12 @@
         <v>174.1</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="V45" s="11" t="n">
+      <c r="V45" s="8" t="n">
         <v>158.1</v>
       </c>
       <c r="W45" s="8" t="n">
@@ -4358,8 +4357,8 @@
       <c r="P46" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="8" t="n">
-        <v>28.8</v>
+      <c r="Q46" s="9" t="n">
+        <v>228.8</v>
       </c>
       <c r="R46" s="8" t="n">
         <v>24.8</v>
@@ -4373,7 +4372,7 @@
       <c r="U46" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V46" s="11" t="n">
+      <c r="V46" s="8" t="n">
         <v>26.3</v>
       </c>
       <c r="W46" s="8" t="n">
@@ -4383,7 +4382,7 @@
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>5.7</v>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_correct_values.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_correct_values.xlsx
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>122.3</v>
+        <v>422.3</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>34.2</v>
@@ -1163,7 +1163,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>20.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1783.5</v>
+        <v>178.3</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>164.8</v>
@@ -1248,7 +1248,7 @@
         <v>388.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>22.8</v>
+        <v>41.6</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1287,9 +1287,7 @@
       <c r="J10" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K10" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="8" t="n">
         <v>20</v>
       </c>
@@ -1883,7 +1881,7 @@
         <v>3.9</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>22.1</v>
@@ -2296,7 +2294,7 @@
         <v>27</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>118.2</v>
+        <v>16.8</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>19.8</v>
@@ -2310,8 +2308,8 @@
       <c r="K22" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="L22" s="10" t="n">
-        <v>22.13</v>
+      <c r="L22" s="3" t="n">
+        <v>21.3</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>21</v>
@@ -2673,10 +2671,10 @@
         <v>28</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>28.2</v>
+        <v>92</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>22.9</v>
+        <v>2</v>
       </c>
       <c r="V26" s="8" t="n">
         <v>23.8</v>
@@ -2743,7 +2741,7 @@
         <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0.4</v>
@@ -2810,7 +2808,7 @@
         <v>18.9</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.8</v>
@@ -3006,8 +3004,8 @@
       <c r="Q30" s="8" t="n">
         <v>135.8</v>
       </c>
-      <c r="R30" s="9" t="n">
-        <v>1207.2</v>
+      <c r="R30" s="8" t="n">
+        <v>120.7</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>140.9</v>
@@ -3016,7 +3014,7 @@
         <v>396.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>26</v>
+        <v>10.5</v>
       </c>
       <c r="V30" s="8" t="n">
         <v>126.1</v>
@@ -3047,7 +3045,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>211.2</v>
+        <v>21.1</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>29</v>
@@ -3068,7 +3066,7 @@
         <v>1.4</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="8" t="n">
@@ -3099,7 +3097,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>18.1</v>
+        <v>8.1</v>
       </c>
       <c r="V31" s="8" t="n">
         <v>25.2</v>
@@ -3189,7 +3187,7 @@
       <c r="V32" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3274,7 +3272,7 @@
       <c r="V33" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3359,7 +3357,7 @@
       <c r="V34" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3444,8 +3442,8 @@
       <c r="V35" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="W35" s="3" t="n">
-        <v>26.6</v>
+      <c r="W35" s="8" t="n">
+        <v>24.6</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>28.9</v>
@@ -3529,7 +3527,7 @@
       <c r="V36" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3573,7 +3571,7 @@
         <v>96.5</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>110.1</v>
+        <v>10.1</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>18.1</v>
@@ -3614,14 +3612,14 @@
       <c r="V37" s="8" t="n">
         <v>136.8</v>
       </c>
-      <c r="W37" s="9" t="n">
+      <c r="W37" s="8" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>142.4</v>
+        <v>182.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>392.2</v>
+        <v>398.2</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>39.7</v>
@@ -3697,7 +3695,7 @@
       <c r="V38" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3729,7 +3727,7 @@
         <v>31.9</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="F39" s="8" t="n">
         <v>26.1</v>
@@ -3874,7 +3872,7 @@
         <v>26.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>10.4</v>
@@ -4231,16 +4229,16 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2026.2</v>
+        <v>202.6</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>190.6</v>
       </c>
-      <c r="E45" s="9" t="n">
-        <v>1215.2</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>156.3</v>
+      <c r="E45" s="8" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>156.1</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>69.09999999999999</v>
@@ -4340,7 +4338,7 @@
         <v>3.1</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="8" t="n">
         <v>21.1</v>
@@ -4357,8 +4355,8 @@
       <c r="P46" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="9" t="n">
-        <v>228.8</v>
+      <c r="Q46" s="8" t="n">
+        <v>28.8</v>
       </c>
       <c r="R46" s="8" t="n">
         <v>24.8</v>
@@ -4382,7 +4380,7 @@
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>83.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>5.7</v>
